--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -5665,22 +5665,22 @@
         </is>
       </c>
       <c r="U3" s="14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="V3" s="14" t="n">
         <v>4.2</v>
       </c>
       <c r="W3" s="14" t="n">
-        <v>454.5</v>
+        <v>45.5</v>
       </c>
       <c r="X3" s="14" t="n">
-        <v>892.9</v>
+        <v>89.3</v>
       </c>
       <c r="Y3" s="14" t="n">
-        <v>781.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Z3" s="14" t="n">
-        <v>454545.5</v>
+        <v>455</v>
       </c>
       <c r="AA3" s="14" t="n"/>
       <c r="AB3" s="14" t="n">
@@ -5689,9 +5689,15 @@
       <c r="AC3" s="14" t="n">
         <v>425</v>
       </c>
-      <c r="AD3" s="14" t="n"/>
-      <c r="AE3" s="14" t="n"/>
-      <c r="AF3" s="14" t="n"/>
+      <c r="AD3" s="14" t="n">
+        <v>725</v>
+      </c>
+      <c r="AE3" s="14" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AF3" s="14" t="n">
+        <v>172</v>
+      </c>
       <c r="AG3" s="14" t="n">
         <v>600</v>
       </c>
@@ -5707,12 +5713,24 @@
       <c r="AK3" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="AL3" s="14" t="n"/>
-      <c r="AM3" s="14" t="n"/>
-      <c r="AN3" s="14" t="n"/>
-      <c r="AO3" s="14" t="n"/>
-      <c r="AP3" s="14" t="n"/>
-      <c r="AQ3" s="14" t="n"/>
+      <c r="AL3" s="14" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AM3" s="14" t="n">
+        <v>180.78</v>
+      </c>
+      <c r="AN3" s="14" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="AO3" s="14" t="n">
+        <v>2533</v>
+      </c>
+      <c r="AP3" s="14" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AQ3" s="14" t="n">
+        <v>1792</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -5780,22 +5798,22 @@
         </is>
       </c>
       <c r="U4" s="11" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="V4" s="11" t="n">
         <v>4.2</v>
       </c>
       <c r="W4" s="11" t="n">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="X4" s="11" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="Y4" s="11" t="n">
-        <v>771.4</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Z4" s="11" t="n">
-        <v>540000</v>
+        <v>540</v>
       </c>
       <c r="AA4" s="11" t="n"/>
       <c r="AB4" s="11" t="n">
@@ -5804,9 +5822,15 @@
       <c r="AC4" s="11" t="n">
         <v>476</v>
       </c>
-      <c r="AD4" s="11" t="n"/>
-      <c r="AE4" s="11" t="n"/>
-      <c r="AF4" s="11" t="n"/>
+      <c r="AD4" s="11" t="n">
+        <v>795</v>
+      </c>
+      <c r="AE4" s="11" t="n">
+        <v>1970</v>
+      </c>
+      <c r="AF4" s="11" t="n">
+        <v>183</v>
+      </c>
       <c r="AG4" s="11" t="n">
         <v>625</v>
       </c>
@@ -5822,12 +5846,24 @@
       <c r="AK4" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="AL4" s="11" t="n"/>
-      <c r="AM4" s="11" t="n"/>
-      <c r="AN4" s="11" t="n"/>
-      <c r="AO4" s="11" t="n"/>
-      <c r="AP4" s="11" t="n"/>
-      <c r="AQ4" s="11" t="n"/>
+      <c r="AL4" s="11" t="n">
+        <v>0.7937</v>
+      </c>
+      <c r="AM4" s="11" t="n">
+        <v>186.66</v>
+      </c>
+      <c r="AN4" s="11" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="AO4" s="11" t="n">
+        <v>2753</v>
+      </c>
+      <c r="AP4" s="11" t="n">
+        <v>1176</v>
+      </c>
+      <c r="AQ4" s="11" t="n">
+        <v>1964</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -5857,23 +5893,49 @@
       <c r="I5" s="14" t="n">
         <v>510</v>
       </c>
-      <c r="J5" s="14" t="n"/>
+      <c r="J5" s="14" t="n">
+        <v>290</v>
+      </c>
       <c r="K5" s="14" t="n"/>
-      <c r="L5" s="14" t="n"/>
-      <c r="M5" s="14" t="n"/>
-      <c r="N5" s="14" t="n"/>
-      <c r="O5" s="14" t="n"/>
-      <c r="P5" s="14" t="n"/>
-      <c r="Q5" s="14" t="n"/>
+      <c r="L5" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P5" s="14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q5" s="14" t="n">
+        <v>0.53</v>
+      </c>
       <c r="R5" s="14" t="n"/>
       <c r="S5" s="14" t="n"/>
       <c r="T5" s="14" t="n"/>
-      <c r="U5" s="14" t="n"/>
-      <c r="V5" s="14" t="n"/>
-      <c r="W5" s="14" t="n"/>
-      <c r="X5" s="14" t="n"/>
-      <c r="Y5" s="14" t="n"/>
-      <c r="Z5" s="14" t="n"/>
+      <c r="U5" s="14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="V5" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W5" s="14" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="X5" s="14" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="Y5" s="14" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="Z5" s="14" t="n">
+        <v>547</v>
+      </c>
       <c r="AA5" s="14" t="n"/>
       <c r="AB5" s="14" t="n">
         <v>1205</v>
@@ -5881,9 +5943,15 @@
       <c r="AC5" s="14" t="n">
         <v>520</v>
       </c>
-      <c r="AD5" s="14" t="n"/>
-      <c r="AE5" s="14" t="n"/>
-      <c r="AF5" s="14" t="n"/>
+      <c r="AD5" s="14" t="n">
+        <v>862.5</v>
+      </c>
+      <c r="AE5" s="14" t="n">
+        <v>2099</v>
+      </c>
+      <c r="AF5" s="14" t="n">
+        <v>195</v>
+      </c>
       <c r="AG5" s="14" t="n">
         <v>650</v>
       </c>
@@ -5899,12 +5967,24 @@
       <c r="AK5" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="AL5" s="14" t="n"/>
-      <c r="AM5" s="14" t="n"/>
-      <c r="AN5" s="14" t="n"/>
-      <c r="AO5" s="14" t="n"/>
-      <c r="AP5" s="14" t="n"/>
-      <c r="AQ5" s="14" t="n"/>
+      <c r="AL5" s="14" t="n">
+        <v>0.8157</v>
+      </c>
+      <c r="AM5" s="14" t="n">
+        <v>216.05</v>
+      </c>
+      <c r="AN5" s="14" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="AO5" s="14" t="n">
+        <v>2978</v>
+      </c>
+      <c r="AP5" s="14" t="n">
+        <v>1285</v>
+      </c>
+      <c r="AQ5" s="14" t="n">
+        <v>2131</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -5972,22 +6052,22 @@
         </is>
       </c>
       <c r="U6" s="11" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="V6" s="11" t="n">
         <v>4.1</v>
       </c>
       <c r="W6" s="11" t="n">
-        <v>476.9</v>
+        <v>47.7</v>
       </c>
       <c r="X6" s="11" t="n">
-        <v>968.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y6" s="11" t="n">
-        <v>815.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="Z6" s="11" t="n">
-        <v>563636.4</v>
+        <v>564</v>
       </c>
       <c r="AA6" s="11" t="n"/>
       <c r="AB6" s="11" t="n">
@@ -5996,9 +6076,15 @@
       <c r="AC6" s="11" t="n">
         <v>617</v>
       </c>
-      <c r="AD6" s="11" t="n"/>
-      <c r="AE6" s="11" t="n"/>
-      <c r="AF6" s="11" t="n"/>
+      <c r="AD6" s="11" t="n">
+        <v>1013.5</v>
+      </c>
+      <c r="AE6" s="11" t="n">
+        <v>2239</v>
+      </c>
+      <c r="AF6" s="11" t="n">
+        <v>208</v>
+      </c>
       <c r="AG6" s="11" t="n">
         <v>700</v>
       </c>
@@ -6014,12 +6100,24 @@
       <c r="AK6" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="AL6" s="11" t="n"/>
-      <c r="AM6" s="11" t="n"/>
-      <c r="AN6" s="11" t="n"/>
-      <c r="AO6" s="11" t="n"/>
-      <c r="AP6" s="11" t="n"/>
-      <c r="AQ6" s="11" t="n"/>
+      <c r="AL6" s="11" t="n">
+        <v>1.1023</v>
+      </c>
+      <c r="AM6" s="11" t="n">
+        <v>244.72</v>
+      </c>
+      <c r="AN6" s="11" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="AO6" s="11" t="n">
+        <v>3484</v>
+      </c>
+      <c r="AP6" s="11" t="n">
+        <v>1525</v>
+      </c>
+      <c r="AQ6" s="11" t="n">
+        <v>2504</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -6049,23 +6147,49 @@
       <c r="I7" s="14" t="n">
         <v>640</v>
       </c>
-      <c r="J7" s="14" t="n"/>
+      <c r="J7" s="14" t="n">
+        <v>365</v>
+      </c>
       <c r="K7" s="14" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="14" t="n"/>
-      <c r="N7" s="14" t="n"/>
-      <c r="O7" s="14" t="n"/>
-      <c r="P7" s="14" t="n"/>
-      <c r="Q7" s="14" t="n"/>
+      <c r="L7" s="14" t="n">
+        <v>440</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" s="14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="14" t="n">
+        <v>0.57</v>
+      </c>
       <c r="R7" s="14" t="n"/>
       <c r="S7" s="14" t="n"/>
       <c r="T7" s="14" t="n"/>
-      <c r="U7" s="14" t="n"/>
-      <c r="V7" s="14" t="n"/>
-      <c r="W7" s="14" t="n"/>
-      <c r="X7" s="14" t="n"/>
-      <c r="Y7" s="14" t="n"/>
-      <c r="Z7" s="14" t="n"/>
+      <c r="U7" s="14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="V7" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W7" s="14" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="X7" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="Y7" s="14" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="Z7" s="14" t="n">
+        <v>640</v>
+      </c>
       <c r="AA7" s="14" t="n"/>
       <c r="AB7" s="14" t="n">
         <v>1755</v>
@@ -6073,9 +6197,15 @@
       <c r="AC7" s="14" t="n">
         <v>780</v>
       </c>
-      <c r="AD7" s="14" t="n"/>
-      <c r="AE7" s="14" t="n"/>
-      <c r="AF7" s="14" t="n"/>
+      <c r="AD7" s="14" t="n">
+        <v>1267.5</v>
+      </c>
+      <c r="AE7" s="14" t="n">
+        <v>2390</v>
+      </c>
+      <c r="AF7" s="14" t="n">
+        <v>222</v>
+      </c>
       <c r="AG7" s="14" t="n">
         <v>750</v>
       </c>
@@ -6091,12 +6221,24 @@
       <c r="AK7" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="AL7" s="14" t="n"/>
-      <c r="AM7" s="14" t="n"/>
-      <c r="AN7" s="14" t="n"/>
-      <c r="AO7" s="14" t="n"/>
-      <c r="AP7" s="14" t="n"/>
-      <c r="AQ7" s="14" t="n"/>
+      <c r="AL7" s="14" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="AM7" s="14" t="n">
+        <v>230.75</v>
+      </c>
+      <c r="AN7" s="14" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="AO7" s="14" t="n">
+        <v>4337</v>
+      </c>
+      <c r="AP7" s="14" t="n">
+        <v>1927</v>
+      </c>
+      <c r="AQ7" s="14" t="n">
+        <v>3132</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -6164,22 +6306,22 @@
         </is>
       </c>
       <c r="U8" s="11" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="V8" s="11" t="n">
         <v>4.7</v>
       </c>
       <c r="W8" s="11" t="n">
-        <v>560</v>
+        <v>56</v>
       </c>
       <c r="X8" s="11" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="Y8" s="11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="11" t="n">
-        <v>700000</v>
+        <v>700</v>
       </c>
       <c r="AA8" s="11" t="n"/>
       <c r="AB8" s="11" t="n">
@@ -6188,9 +6330,15 @@
       <c r="AC8" s="11" t="n">
         <v>915</v>
       </c>
-      <c r="AD8" s="11" t="n"/>
-      <c r="AE8" s="11" t="n"/>
-      <c r="AF8" s="11" t="n"/>
+      <c r="AD8" s="11" t="n">
+        <v>1490.5</v>
+      </c>
+      <c r="AE8" s="11" t="n">
+        <v>2551</v>
+      </c>
+      <c r="AF8" s="11" t="n">
+        <v>237</v>
+      </c>
       <c r="AG8" s="11" t="n">
         <v>780</v>
       </c>
@@ -6206,12 +6354,24 @@
       <c r="AK8" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="AL8" s="11" t="n"/>
-      <c r="AM8" s="11" t="n"/>
-      <c r="AN8" s="11" t="n"/>
-      <c r="AO8" s="11" t="n"/>
-      <c r="AP8" s="11" t="n"/>
-      <c r="AQ8" s="11" t="n"/>
+      <c r="AL8" s="11" t="n">
+        <v>1.3448</v>
+      </c>
+      <c r="AM8" s="11" t="n">
+        <v>278.15</v>
+      </c>
+      <c r="AN8" s="11" t="n">
+        <v>122.43</v>
+      </c>
+      <c r="AO8" s="11" t="n">
+        <v>5105</v>
+      </c>
+      <c r="AP8" s="11" t="n">
+        <v>2261</v>
+      </c>
+      <c r="AQ8" s="11" t="n">
+        <v>3683</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -6241,23 +6401,49 @@
       <c r="I9" s="14" t="n">
         <v>810</v>
       </c>
-      <c r="J9" s="14" t="n"/>
+      <c r="J9" s="14" t="n">
+        <v>335</v>
+      </c>
       <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="14" t="n"/>
-      <c r="Q9" s="14" t="n"/>
+      <c r="L9" s="14" t="n">
+        <v>440</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O9" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q9" s="14" t="n">
+        <v>0.53</v>
+      </c>
       <c r="R9" s="14" t="n"/>
       <c r="S9" s="14" t="n"/>
       <c r="T9" s="14" t="n"/>
-      <c r="U9" s="14" t="n"/>
-      <c r="V9" s="14" t="n"/>
-      <c r="W9" s="14" t="n"/>
-      <c r="X9" s="14" t="n"/>
-      <c r="Y9" s="14" t="n"/>
-      <c r="Z9" s="14" t="n"/>
+      <c r="U9" s="14" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="V9" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W9" s="14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X9" s="14" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="Y9" s="14" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="Z9" s="14" t="n">
+        <v>632</v>
+      </c>
       <c r="AA9" s="14" t="n"/>
       <c r="AB9" s="14" t="n">
         <v>2147</v>
@@ -6265,9 +6451,15 @@
       <c r="AC9" s="14" t="n">
         <v>980</v>
       </c>
-      <c r="AD9" s="14" t="n"/>
-      <c r="AE9" s="14" t="n"/>
-      <c r="AF9" s="14" t="n"/>
+      <c r="AD9" s="14" t="n">
+        <v>1563.5</v>
+      </c>
+      <c r="AE9" s="14" t="n">
+        <v>2713</v>
+      </c>
+      <c r="AF9" s="14" t="n">
+        <v>252</v>
+      </c>
       <c r="AG9" s="14" t="n">
         <v>820</v>
       </c>
@@ -6283,12 +6475,24 @@
       <c r="AK9" s="14" t="n">
         <v>62</v>
       </c>
-      <c r="AL9" s="14" t="n"/>
-      <c r="AM9" s="14" t="n"/>
-      <c r="AN9" s="14" t="n"/>
-      <c r="AO9" s="14" t="n"/>
-      <c r="AP9" s="14" t="n"/>
-      <c r="AQ9" s="14" t="n"/>
+      <c r="AL9" s="14" t="n">
+        <v>1.3669</v>
+      </c>
+      <c r="AM9" s="14" t="n">
+        <v>245.08</v>
+      </c>
+      <c r="AN9" s="14" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="AO9" s="14" t="n">
+        <v>5305</v>
+      </c>
+      <c r="AP9" s="14" t="n">
+        <v>2422</v>
+      </c>
+      <c r="AQ9" s="14" t="n">
+        <v>3863</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -6356,22 +6560,22 @@
         </is>
       </c>
       <c r="U10" s="11" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="V10" s="11" t="n">
         <v>3.6</v>
       </c>
       <c r="W10" s="11" t="n">
-        <v>431</v>
+        <v>43.1</v>
       </c>
       <c r="X10" s="11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="11" t="n">
-        <v>833.3</v>
+        <v>83.3</v>
       </c>
       <c r="Z10" s="11" t="n">
-        <v>555555.6</v>
+        <v>556</v>
       </c>
       <c r="AA10" s="11" t="n"/>
       <c r="AB10" s="11" t="n">
@@ -6380,9 +6584,15 @@
       <c r="AC10" s="11" t="n">
         <v>925</v>
       </c>
-      <c r="AD10" s="11" t="n"/>
-      <c r="AE10" s="11" t="n"/>
-      <c r="AF10" s="11" t="n"/>
+      <c r="AD10" s="11" t="n">
+        <v>1449.5</v>
+      </c>
+      <c r="AE10" s="11" t="n">
+        <v>2885</v>
+      </c>
+      <c r="AF10" s="11" t="n">
+        <v>268</v>
+      </c>
       <c r="AG10" s="11" t="n">
         <v>850</v>
       </c>
@@ -6398,12 +6608,24 @@
       <c r="AK10" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="AL10" s="11" t="n"/>
-      <c r="AM10" s="11" t="n"/>
-      <c r="AN10" s="11" t="n"/>
-      <c r="AO10" s="11" t="n"/>
-      <c r="AP10" s="11" t="n"/>
-      <c r="AQ10" s="11" t="n"/>
+      <c r="AL10" s="11" t="n">
+        <v>1.3007</v>
+      </c>
+      <c r="AM10" s="11" t="n">
+        <v>209.81</v>
+      </c>
+      <c r="AN10" s="11" t="n">
+        <v>105.51</v>
+      </c>
+      <c r="AO10" s="11" t="n">
+        <v>4878</v>
+      </c>
+      <c r="AP10" s="11" t="n">
+        <v>2286</v>
+      </c>
+      <c r="AQ10" s="11" t="n">
+        <v>3582</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -6433,23 +6655,49 @@
       <c r="I11" s="14" t="n">
         <v>880</v>
       </c>
-      <c r="J11" s="14" t="n"/>
+      <c r="J11" s="14" t="n">
+        <v>260</v>
+      </c>
       <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="n"/>
-      <c r="N11" s="14" t="n"/>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="14" t="n"/>
-      <c r="Q11" s="14" t="n"/>
+      <c r="L11" s="14" t="n">
+        <v>403.33</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="O11" s="14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P11" s="14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q11" s="14" t="n">
+        <v>0.46</v>
+      </c>
       <c r="R11" s="14" t="n"/>
       <c r="S11" s="14" t="n"/>
       <c r="T11" s="14" t="n"/>
-      <c r="U11" s="14" t="n"/>
-      <c r="V11" s="14" t="n"/>
-      <c r="W11" s="14" t="n"/>
-      <c r="X11" s="14" t="n"/>
-      <c r="Y11" s="14" t="n"/>
-      <c r="Z11" s="14" t="n"/>
+      <c r="U11" s="14" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="V11" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W11" s="14" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="X11" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y11" s="14" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="Z11" s="14" t="n">
+        <v>565</v>
+      </c>
       <c r="AA11" s="14" t="n"/>
       <c r="AB11" s="14" t="n">
         <v>1679</v>
@@ -6457,9 +6705,15 @@
       <c r="AC11" s="14" t="n">
         <v>807</v>
       </c>
-      <c r="AD11" s="14" t="n"/>
-      <c r="AE11" s="14" t="n"/>
-      <c r="AF11" s="14" t="n"/>
+      <c r="AD11" s="14" t="n">
+        <v>1243</v>
+      </c>
+      <c r="AE11" s="14" t="n">
+        <v>3068</v>
+      </c>
+      <c r="AF11" s="14" t="n">
+        <v>285</v>
+      </c>
       <c r="AG11" s="14" t="n">
         <v>875</v>
       </c>
@@ -6475,12 +6729,24 @@
       <c r="AK11" s="14" t="n">
         <v>61</v>
       </c>
-      <c r="AL11" s="14" t="n"/>
-      <c r="AM11" s="14" t="n"/>
-      <c r="AN11" s="14" t="n"/>
-      <c r="AO11" s="14" t="n"/>
-      <c r="AP11" s="14" t="n"/>
-      <c r="AQ11" s="14" t="n"/>
+      <c r="AL11" s="14" t="n">
+        <v>1.3448</v>
+      </c>
+      <c r="AM11" s="14" t="n">
+        <v>287.71</v>
+      </c>
+      <c r="AN11" s="14" t="n">
+        <v>125.98</v>
+      </c>
+      <c r="AO11" s="14" t="n">
+        <v>4149</v>
+      </c>
+      <c r="AP11" s="14" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AQ11" s="14" t="n">
+        <v>3072</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -6510,23 +6776,49 @@
       <c r="I12" s="11" t="n">
         <v>930</v>
       </c>
-      <c r="J12" s="11" t="n"/>
+      <c r="J12" s="11" t="n">
+        <v>270</v>
+      </c>
       <c r="K12" s="11" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
-      <c r="N12" s="11" t="n"/>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="n"/>
-      <c r="Q12" s="11" t="n"/>
+      <c r="L12" s="11" t="n">
+        <v>426.67</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q12" s="11" t="n">
+        <v>0.47</v>
+      </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="11" t="n"/>
       <c r="T12" s="11" t="n"/>
-      <c r="U12" s="11" t="n"/>
-      <c r="V12" s="11" t="n"/>
-      <c r="W12" s="11" t="n"/>
-      <c r="X12" s="11" t="n"/>
-      <c r="Y12" s="11" t="n"/>
-      <c r="Z12" s="11" t="n"/>
+      <c r="U12" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V12" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W12" s="11" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="X12" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y12" s="11" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Z12" s="11" t="n">
+        <v>574</v>
+      </c>
       <c r="AA12" s="11" t="n"/>
       <c r="AB12" s="11" t="n">
         <v>1538</v>
@@ -6534,9 +6826,15 @@
       <c r="AC12" s="11" t="n">
         <v>738</v>
       </c>
-      <c r="AD12" s="11" t="n"/>
-      <c r="AE12" s="11" t="n"/>
-      <c r="AF12" s="11" t="n"/>
+      <c r="AD12" s="11" t="n">
+        <v>1138</v>
+      </c>
+      <c r="AE12" s="11" t="n">
+        <v>3251</v>
+      </c>
+      <c r="AF12" s="11" t="n">
+        <v>302</v>
+      </c>
       <c r="AG12" s="11" t="n">
         <v>900</v>
       </c>
@@ -6552,12 +6850,24 @@
       <c r="AK12" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="AL12" s="11" t="n"/>
-      <c r="AM12" s="11" t="n"/>
-      <c r="AN12" s="11" t="n"/>
-      <c r="AO12" s="11" t="n"/>
-      <c r="AP12" s="11" t="n"/>
-      <c r="AQ12" s="11" t="n"/>
+      <c r="AL12" s="11" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="AM12" s="11" t="n">
+        <v>214.58</v>
+      </c>
+      <c r="AN12" s="11" t="n">
+        <v>103.54</v>
+      </c>
+      <c r="AO12" s="11" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AP12" s="11" t="n">
+        <v>1824</v>
+      </c>
+      <c r="AQ12" s="11" t="n">
+        <v>2812</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -6625,22 +6935,22 @@
         </is>
       </c>
       <c r="U13" s="14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="V13" s="14" t="n">
         <v>3.5</v>
       </c>
       <c r="W13" s="14" t="n">
-        <v>430.8</v>
+        <v>43.1</v>
       </c>
       <c r="X13" s="14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Y13" s="14" t="n">
-        <v>848.5</v>
+        <v>84.8</v>
       </c>
       <c r="Z13" s="14" t="n">
-        <v>583333.3</v>
+        <v>583</v>
       </c>
       <c r="AA13" s="14" t="n"/>
       <c r="AB13" s="14" t="n">
@@ -6649,8 +6959,12 @@
       <c r="AC13" s="14" t="n">
         <v>632</v>
       </c>
-      <c r="AD13" s="14" t="n"/>
-      <c r="AE13" s="14" t="n"/>
+      <c r="AD13" s="14" t="n">
+        <v>934</v>
+      </c>
+      <c r="AE13" s="14" t="n">
+        <v>3391</v>
+      </c>
       <c r="AF13" s="14" t="n">
         <v>315</v>
       </c>
@@ -6669,12 +6983,24 @@
       <c r="AK13" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="AL13" s="14" t="n"/>
-      <c r="AM13" s="14" t="n"/>
-      <c r="AN13" s="14" t="n"/>
-      <c r="AO13" s="14" t="n"/>
-      <c r="AP13" s="14" t="n"/>
-      <c r="AQ13" s="14" t="n"/>
+      <c r="AL13" s="14" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="AM13" s="14" t="n">
+        <v>185.56</v>
+      </c>
+      <c r="AN13" s="14" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="AO13" s="14" t="n">
+        <v>3054</v>
+      </c>
+      <c r="AP13" s="14" t="n">
+        <v>1562</v>
+      </c>
+      <c r="AQ13" s="14" t="n">
+        <v>2308</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -6704,23 +7030,49 @@
       <c r="I14" s="11" t="n">
         <v>1050</v>
       </c>
-      <c r="J14" s="11" t="n"/>
+      <c r="J14" s="11" t="n">
+        <v>270</v>
+      </c>
       <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="n"/>
-      <c r="P14" s="11" t="n"/>
-      <c r="Q14" s="11" t="n"/>
+      <c r="L14" s="11" t="n">
+        <v>435</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q14" s="11" t="n">
+        <v>0.46</v>
+      </c>
       <c r="R14" s="11" t="n"/>
       <c r="S14" s="11" t="n"/>
       <c r="T14" s="11" t="n"/>
-      <c r="U14" s="11" t="n"/>
-      <c r="V14" s="11" t="n"/>
-      <c r="W14" s="11" t="n"/>
-      <c r="X14" s="11" t="n"/>
-      <c r="Y14" s="11" t="n"/>
-      <c r="Z14" s="11" t="n"/>
+      <c r="U14" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V14" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W14" s="11" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="X14" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y14" s="11" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Z14" s="11" t="n">
+        <v>587</v>
+      </c>
       <c r="AA14" s="11" t="n"/>
       <c r="AB14" s="11" t="n">
         <v>1020</v>
@@ -6728,8 +7080,12 @@
       <c r="AC14" s="11" t="n">
         <v>515</v>
       </c>
-      <c r="AD14" s="11" t="n"/>
-      <c r="AE14" s="11" t="n"/>
+      <c r="AD14" s="11" t="n">
+        <v>767.5</v>
+      </c>
+      <c r="AE14" s="11" t="n">
+        <v>3531</v>
+      </c>
       <c r="AF14" s="11" t="n">
         <v>328</v>
       </c>
@@ -6748,12 +7104,24 @@
       <c r="AK14" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="AL14" s="11" t="n"/>
-      <c r="AM14" s="11" t="n"/>
-      <c r="AN14" s="11" t="n"/>
-      <c r="AO14" s="11" t="n"/>
-      <c r="AP14" s="11" t="n"/>
-      <c r="AQ14" s="11" t="n"/>
+      <c r="AL14" s="11" t="n">
+        <v>1.1464</v>
+      </c>
+      <c r="AM14" s="11" t="n">
+        <v>175.64</v>
+      </c>
+      <c r="AN14" s="11" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="AO14" s="11" t="n">
+        <v>2520</v>
+      </c>
+      <c r="AP14" s="11" t="n">
+        <v>1273</v>
+      </c>
+      <c r="AQ14" s="11" t="n">
+        <v>1897</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -6821,22 +7189,22 @@
         </is>
       </c>
       <c r="U15" s="14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="V15" s="14" t="n">
         <v>3.5</v>
       </c>
       <c r="W15" s="14" t="n">
-        <v>433.3</v>
+        <v>43.3</v>
       </c>
       <c r="X15" s="14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Y15" s="14" t="n">
-        <v>838.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z15" s="14" t="n">
-        <v>577777.8</v>
+        <v>578</v>
       </c>
       <c r="AA15" s="14" t="n"/>
       <c r="AB15" s="14" t="n">
@@ -6845,8 +7213,12 @@
       <c r="AC15" s="14" t="n">
         <v>462</v>
       </c>
-      <c r="AD15" s="14" t="n"/>
-      <c r="AE15" s="14" t="n"/>
+      <c r="AD15" s="14" t="n">
+        <v>693</v>
+      </c>
+      <c r="AE15" s="14" t="n">
+        <v>3972</v>
+      </c>
       <c r="AF15" s="14" t="n">
         <v>369</v>
       </c>
@@ -6865,12 +7237,24 @@
       <c r="AK15" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="AL15" s="14" t="n"/>
-      <c r="AM15" s="14" t="n"/>
-      <c r="AN15" s="14" t="n"/>
-      <c r="AO15" s="14" t="n"/>
-      <c r="AP15" s="14" t="n"/>
-      <c r="AQ15" s="14" t="n"/>
+      <c r="AL15" s="14" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="AM15" s="14" t="n">
+        <v>216.05</v>
+      </c>
+      <c r="AN15" s="14" t="n">
+        <v>76.37</v>
+      </c>
+      <c r="AO15" s="14" t="n">
+        <v>2283</v>
+      </c>
+      <c r="AP15" s="14" t="n">
+        <v>1142</v>
+      </c>
+      <c r="AQ15" s="14" t="n">
+        <v>1712</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
@@ -6900,23 +7284,49 @@
       <c r="I16" s="11" t="n">
         <v>1350</v>
       </c>
-      <c r="J16" s="11" t="n"/>
+      <c r="J16" s="11" t="n">
+        <v>240</v>
+      </c>
       <c r="K16" s="11" t="n"/>
-      <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
-      <c r="N16" s="11" t="n"/>
-      <c r="O16" s="11" t="n"/>
-      <c r="P16" s="11" t="n"/>
-      <c r="Q16" s="11" t="n"/>
+      <c r="L16" s="11" t="n">
+        <v>413.33</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q16" s="11" t="n">
+        <v>0.43</v>
+      </c>
       <c r="R16" s="11" t="n"/>
       <c r="S16" s="11" t="n"/>
       <c r="T16" s="11" t="n"/>
-      <c r="U16" s="11" t="n"/>
-      <c r="V16" s="11" t="n"/>
-      <c r="W16" s="11" t="n"/>
-      <c r="X16" s="11" t="n"/>
-      <c r="Y16" s="11" t="n"/>
-      <c r="Z16" s="11" t="n"/>
+      <c r="U16" s="11" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="V16" s="11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W16" s="11" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="X16" s="11" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="Y16" s="11" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="Z16" s="11" t="n">
+        <v>558</v>
+      </c>
       <c r="AA16" s="11" t="n"/>
       <c r="AB16" s="11" t="n">
         <v>862</v>
@@ -6924,8 +7334,12 @@
       <c r="AC16" s="11" t="n">
         <v>440</v>
       </c>
-      <c r="AD16" s="11" t="n"/>
-      <c r="AE16" s="11" t="n"/>
+      <c r="AD16" s="11" t="n">
+        <v>651</v>
+      </c>
+      <c r="AE16" s="11" t="n">
+        <v>3961</v>
+      </c>
       <c r="AF16" s="11" t="n">
         <v>368</v>
       </c>
@@ -6944,12 +7358,24 @@
       <c r="AK16" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="AL16" s="11" t="n"/>
-      <c r="AM16" s="11" t="n"/>
-      <c r="AN16" s="11" t="n"/>
-      <c r="AO16" s="11" t="n"/>
-      <c r="AP16" s="11" t="n"/>
-      <c r="AQ16" s="11" t="n"/>
+      <c r="AL16" s="11" t="n">
+        <v>1.4992</v>
+      </c>
+      <c r="AM16" s="11" t="n">
+        <v>271.91</v>
+      </c>
+      <c r="AN16" s="11" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="AO16" s="11" t="n">
+        <v>2130</v>
+      </c>
+      <c r="AP16" s="11" t="n">
+        <v>1087</v>
+      </c>
+      <c r="AQ16" s="11" t="n">
+        <v>1609</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n">
@@ -6979,23 +7405,49 @@
       <c r="I17" s="14" t="n">
         <v>1500</v>
       </c>
-      <c r="J17" s="14" t="n"/>
+      <c r="J17" s="14" t="n">
+        <v>220</v>
+      </c>
       <c r="K17" s="14" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
+      <c r="L17" s="14" t="n">
+        <v>406.67</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="O17" s="14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q17" s="14" t="n">
+        <v>0.42</v>
+      </c>
       <c r="R17" s="14" t="n"/>
       <c r="S17" s="14" t="n"/>
       <c r="T17" s="14" t="n"/>
-      <c r="U17" s="14" t="n"/>
-      <c r="V17" s="14" t="n"/>
-      <c r="W17" s="14" t="n"/>
-      <c r="X17" s="14" t="n"/>
-      <c r="Y17" s="14" t="n"/>
-      <c r="Z17" s="14" t="n"/>
+      <c r="U17" s="14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="V17" s="14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W17" s="14" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="X17" s="14" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="Y17" s="14" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="Z17" s="14" t="n">
+        <v>524</v>
+      </c>
       <c r="AA17" s="14" t="n"/>
       <c r="AB17" s="14" t="n">
         <v>852</v>
@@ -7003,8 +7455,12 @@
       <c r="AC17" s="14" t="n">
         <v>435</v>
       </c>
-      <c r="AD17" s="14" t="n"/>
-      <c r="AE17" s="14" t="n"/>
+      <c r="AD17" s="14" t="n">
+        <v>643.5</v>
+      </c>
+      <c r="AE17" s="14" t="n">
+        <v>3950</v>
+      </c>
       <c r="AF17" s="14" t="n">
         <v>367</v>
       </c>
@@ -7023,12 +7479,24 @@
       <c r="AK17" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="AL17" s="14" t="n"/>
-      <c r="AM17" s="14" t="n"/>
-      <c r="AN17" s="14" t="n"/>
-      <c r="AO17" s="14" t="n"/>
-      <c r="AP17" s="14" t="n"/>
-      <c r="AQ17" s="14" t="n"/>
+      <c r="AL17" s="14" t="n">
+        <v>1.5432</v>
+      </c>
+      <c r="AM17" s="14" t="n">
+        <v>209.07</v>
+      </c>
+      <c r="AN17" s="14" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="AO17" s="14" t="n">
+        <v>2105</v>
+      </c>
+      <c r="AP17" s="14" t="n">
+        <v>1075</v>
+      </c>
+      <c r="AQ17" s="14" t="n">
+        <v>1590</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
@@ -7102,16 +7570,16 @@
         <v>2.9</v>
       </c>
       <c r="W18" s="11" t="n">
-        <v>363.6</v>
+        <v>36.4</v>
       </c>
       <c r="X18" s="11" t="n">
-        <v>833.3</v>
+        <v>83.3</v>
       </c>
       <c r="Y18" s="11" t="n">
-        <v>689.7</v>
+        <v>69</v>
       </c>
       <c r="Z18" s="11" t="n">
-        <v>500000</v>
+        <v>500</v>
       </c>
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="n">
@@ -7120,8 +7588,12 @@
       <c r="AC18" s="11" t="n">
         <v>415</v>
       </c>
-      <c r="AD18" s="11" t="n"/>
-      <c r="AE18" s="11" t="n"/>
+      <c r="AD18" s="11" t="n">
+        <v>601</v>
+      </c>
+      <c r="AE18" s="11" t="n">
+        <v>4026</v>
+      </c>
       <c r="AF18" s="11" t="n">
         <v>374</v>
       </c>
@@ -7140,12 +7612,24 @@
       <c r="AK18" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="AL18" s="11" t="n"/>
-      <c r="AM18" s="11" t="n"/>
-      <c r="AN18" s="11" t="n"/>
-      <c r="AO18" s="11" t="n"/>
-      <c r="AP18" s="11" t="n"/>
-      <c r="AQ18" s="11" t="n"/>
+      <c r="AL18" s="11" t="n">
+        <v>1.6314</v>
+      </c>
+      <c r="AM18" s="11" t="n">
+        <v>210.91</v>
+      </c>
+      <c r="AN18" s="11" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="AO18" s="11" t="n">
+        <v>1945</v>
+      </c>
+      <c r="AP18" s="11" t="n">
+        <v>1025</v>
+      </c>
+      <c r="AQ18" s="11" t="n">
+        <v>1485</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n">
@@ -7213,22 +7697,22 @@
         </is>
       </c>
       <c r="U19" s="14" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="V19" s="14" t="n">
         <v>3.5</v>
       </c>
       <c r="W19" s="14" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="X19" s="14" t="n">
-        <v>1166.7</v>
+        <v>116.7</v>
       </c>
       <c r="Y19" s="14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z19" s="14" t="n">
-        <v>636363.6</v>
+        <v>636</v>
       </c>
       <c r="AA19" s="14" t="n"/>
       <c r="AB19" s="14" t="n">
@@ -7237,8 +7721,12 @@
       <c r="AC19" s="14" t="n">
         <v>413</v>
       </c>
-      <c r="AD19" s="14" t="n"/>
-      <c r="AE19" s="14" t="n"/>
+      <c r="AD19" s="14" t="n">
+        <v>591</v>
+      </c>
+      <c r="AE19" s="14" t="n">
+        <v>3627</v>
+      </c>
       <c r="AF19" s="14" t="n">
         <v>337</v>
       </c>
@@ -7257,12 +7745,24 @@
       <c r="AK19" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="AL19" s="14" t="n"/>
-      <c r="AM19" s="14" t="n"/>
-      <c r="AN19" s="14" t="n"/>
-      <c r="AO19" s="14" t="n"/>
-      <c r="AP19" s="14" t="n"/>
-      <c r="AQ19" s="14" t="n"/>
+      <c r="AL19" s="14" t="n">
+        <v>1.5873</v>
+      </c>
+      <c r="AM19" s="14" t="n">
+        <v>205.03</v>
+      </c>
+      <c r="AN19" s="14" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AO19" s="14" t="n">
+        <v>1900</v>
+      </c>
+      <c r="AP19" s="14" t="n">
+        <v>1021</v>
+      </c>
+      <c r="AQ19" s="14" t="n">
+        <v>1460</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
@@ -7292,23 +7792,49 @@
       <c r="I20" s="11" t="n">
         <v>1750</v>
       </c>
-      <c r="J20" s="11" t="n"/>
+      <c r="J20" s="11" t="n">
+        <v>425</v>
+      </c>
       <c r="K20" s="11" t="n"/>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="11" t="n"/>
-      <c r="P20" s="11" t="n"/>
-      <c r="Q20" s="11" t="n"/>
+      <c r="L20" s="11" t="n">
+        <v>700</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>115</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q20" s="11" t="n">
+        <v>0.6</v>
+      </c>
       <c r="R20" s="11" t="n"/>
       <c r="S20" s="11" t="n"/>
       <c r="T20" s="11" t="n"/>
-      <c r="U20" s="11" t="n"/>
-      <c r="V20" s="11" t="n"/>
-      <c r="W20" s="11" t="n"/>
-      <c r="X20" s="11" t="n"/>
-      <c r="Y20" s="11" t="n"/>
-      <c r="Z20" s="11" t="n"/>
+      <c r="U20" s="11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="V20" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W20" s="11" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="X20" s="11" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="Y20" s="11" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="Z20" s="11" t="n">
+        <v>708</v>
+      </c>
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="n">
         <v>766</v>
@@ -7316,8 +7842,12 @@
       <c r="AC20" s="11" t="n">
         <v>413</v>
       </c>
-      <c r="AD20" s="11" t="n"/>
-      <c r="AE20" s="11" t="n"/>
+      <c r="AD20" s="11" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="AE20" s="11" t="n">
+        <v>3897</v>
+      </c>
       <c r="AF20" s="11" t="n">
         <v>362</v>
       </c>
@@ -7336,12 +7866,24 @@
       <c r="AK20" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="AL20" s="11" t="n"/>
-      <c r="AM20" s="11" t="n"/>
-      <c r="AN20" s="11" t="n"/>
-      <c r="AO20" s="11" t="n"/>
-      <c r="AP20" s="11" t="n"/>
-      <c r="AQ20" s="11" t="n"/>
+      <c r="AL20" s="11" t="n">
+        <v>1.5653</v>
+      </c>
+      <c r="AM20" s="11" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="AN20" s="11" t="n">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="AO20" s="11" t="n">
+        <v>1893</v>
+      </c>
+      <c r="AP20" s="11" t="n">
+        <v>1021</v>
+      </c>
+      <c r="AQ20" s="11" t="n">
+        <v>1457</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n">
@@ -7409,22 +7951,22 @@
         </is>
       </c>
       <c r="U21" s="14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="V21" s="14" t="n">
         <v>3.8</v>
       </c>
       <c r="W21" s="14" t="n">
-        <v>641</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>1515.2</v>
+        <v>151.5</v>
       </c>
       <c r="Y21" s="14" t="n">
-        <v>1315.8</v>
+        <v>131.6</v>
       </c>
       <c r="Z21" s="14" t="n">
-        <v>769230.8</v>
+        <v>769</v>
       </c>
       <c r="AA21" s="14" t="n"/>
       <c r="AB21" s="14" t="n">
@@ -7433,8 +7975,12 @@
       <c r="AC21" s="14" t="n">
         <v>430</v>
       </c>
-      <c r="AD21" s="14" t="n"/>
-      <c r="AE21" s="14" t="n"/>
+      <c r="AD21" s="14" t="n">
+        <v>617</v>
+      </c>
+      <c r="AE21" s="14" t="n">
+        <v>3111</v>
+      </c>
       <c r="AF21" s="14" t="n">
         <v>289</v>
       </c>
@@ -7453,12 +7999,24 @@
       <c r="AK21" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="AL21" s="14" t="n"/>
-      <c r="AM21" s="14" t="n"/>
-      <c r="AN21" s="14" t="n"/>
-      <c r="AO21" s="14" t="n"/>
-      <c r="AP21" s="14" t="n"/>
-      <c r="AQ21" s="14" t="n"/>
+      <c r="AL21" s="14" t="n">
+        <v>1.5873</v>
+      </c>
+      <c r="AM21" s="14" t="n">
+        <v>235.16</v>
+      </c>
+      <c r="AN21" s="14" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="AO21" s="14" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AP21" s="14" t="n">
+        <v>1063</v>
+      </c>
+      <c r="AQ21" s="14" t="n">
+        <v>1525</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
@@ -7488,23 +8046,49 @@
       <c r="I22" s="11" t="n">
         <v>1900</v>
       </c>
-      <c r="J22" s="11" t="n"/>
+      <c r="J22" s="11" t="n">
+        <v>525</v>
+      </c>
       <c r="K22" s="11" t="n"/>
-      <c r="L22" s="11" t="n"/>
-      <c r="M22" s="11" t="n"/>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="11" t="n"/>
-      <c r="P22" s="11" t="n"/>
-      <c r="Q22" s="11" t="n"/>
+      <c r="L22" s="11" t="n">
+        <v>850</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>135</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>0.68</v>
+      </c>
       <c r="R22" s="11" t="n"/>
       <c r="S22" s="11" t="n"/>
       <c r="T22" s="11" t="n"/>
-      <c r="U22" s="11" t="n"/>
-      <c r="V22" s="11" t="n"/>
-      <c r="W22" s="11" t="n"/>
-      <c r="X22" s="11" t="n"/>
-      <c r="Y22" s="11" t="n"/>
-      <c r="Z22" s="11" t="n"/>
+      <c r="U22" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V22" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W22" s="11" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="X22" s="11" t="n">
+        <v>154.4</v>
+      </c>
+      <c r="Y22" s="11" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="Z22" s="11" t="n">
+        <v>772</v>
+      </c>
       <c r="AA22" s="11" t="n"/>
       <c r="AB22" s="11" t="n">
         <v>851</v>
@@ -7512,8 +8096,12 @@
       <c r="AC22" s="11" t="n">
         <v>453</v>
       </c>
-      <c r="AD22" s="11" t="n"/>
-      <c r="AE22" s="11" t="n"/>
+      <c r="AD22" s="11" t="n">
+        <v>652</v>
+      </c>
+      <c r="AE22" s="11" t="n">
+        <v>3240</v>
+      </c>
       <c r="AF22" s="11" t="n">
         <v>301</v>
       </c>
@@ -7532,12 +8120,24 @@
       <c r="AK22" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="AL22" s="11" t="n"/>
-      <c r="AM22" s="11" t="n"/>
-      <c r="AN22" s="11" t="n"/>
-      <c r="AO22" s="11" t="n"/>
-      <c r="AP22" s="11" t="n"/>
-      <c r="AQ22" s="11" t="n"/>
+      <c r="AL22" s="11" t="n">
+        <v>1.4992</v>
+      </c>
+      <c r="AM22" s="11" t="n">
+        <v>201.36</v>
+      </c>
+      <c r="AN22" s="11" t="n">
+        <v>88.97</v>
+      </c>
+      <c r="AO22" s="11" t="n">
+        <v>2103</v>
+      </c>
+      <c r="AP22" s="11" t="n">
+        <v>1119</v>
+      </c>
+      <c r="AQ22" s="11" t="n">
+        <v>1611</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n">
@@ -7605,22 +8205,22 @@
         </is>
       </c>
       <c r="U23" s="14" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="V23" s="14" t="n">
         <v>3.9</v>
       </c>
       <c r="W23" s="14" t="n">
-        <v>647.1</v>
+        <v>64.7</v>
       </c>
       <c r="X23" s="14" t="n">
-        <v>1571.4</v>
+        <v>157.1</v>
       </c>
       <c r="Y23" s="14" t="n">
-        <v>1375</v>
+        <v>137.5</v>
       </c>
       <c r="Z23" s="14" t="n">
-        <v>785714.3</v>
+        <v>786</v>
       </c>
       <c r="AA23" s="14" t="n"/>
       <c r="AB23" s="14" t="n">
@@ -7629,8 +8229,12 @@
       <c r="AC23" s="14" t="n">
         <v>480</v>
       </c>
-      <c r="AD23" s="14" t="n"/>
-      <c r="AE23" s="14" t="n"/>
+      <c r="AD23" s="14" t="n">
+        <v>690</v>
+      </c>
+      <c r="AE23" s="14" t="n">
+        <v>3165</v>
+      </c>
       <c r="AF23" s="14" t="n">
         <v>294</v>
       </c>
@@ -7649,12 +8253,24 @@
       <c r="AK23" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="AL23" s="14" t="n"/>
-      <c r="AM23" s="14" t="n"/>
-      <c r="AN23" s="14" t="n"/>
-      <c r="AO23" s="14" t="n"/>
-      <c r="AP23" s="14" t="n"/>
-      <c r="AQ23" s="14" t="n"/>
+      <c r="AL23" s="14" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="AM23" s="14" t="n">
+        <v>246.92</v>
+      </c>
+      <c r="AN23" s="14" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="AO23" s="14" t="n">
+        <v>2224</v>
+      </c>
+      <c r="AP23" s="14" t="n">
+        <v>1186</v>
+      </c>
+      <c r="AQ23" s="14" t="n">
+        <v>1705</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -7684,23 +8300,49 @@
       <c r="I24" s="11" t="n">
         <v>2150</v>
       </c>
-      <c r="J24" s="11" t="n"/>
+      <c r="J24" s="11" t="n">
+        <v>625</v>
+      </c>
       <c r="K24" s="11" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="11" t="n"/>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="11" t="n"/>
-      <c r="P24" s="11" t="n"/>
-      <c r="Q24" s="11" t="n"/>
+      <c r="L24" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q24" s="11" t="n">
+        <v>0.72</v>
+      </c>
       <c r="R24" s="11" t="n"/>
       <c r="S24" s="11" t="n"/>
       <c r="T24" s="11" t="n"/>
-      <c r="U24" s="11" t="n"/>
-      <c r="V24" s="11" t="n"/>
-      <c r="W24" s="11" t="n"/>
-      <c r="X24" s="11" t="n"/>
-      <c r="Y24" s="11" t="n"/>
-      <c r="Z24" s="11" t="n"/>
+      <c r="U24" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V24" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W24" s="11" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="X24" s="11" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="Y24" s="11" t="n">
+        <v>147.1</v>
+      </c>
+      <c r="Z24" s="11" t="n">
+        <v>868</v>
+      </c>
       <c r="AA24" s="11" t="n"/>
       <c r="AB24" s="11" t="n">
         <v>960</v>
@@ -7708,8 +8350,12 @@
       <c r="AC24" s="11" t="n">
         <v>511</v>
       </c>
-      <c r="AD24" s="11" t="n"/>
-      <c r="AE24" s="11" t="n"/>
+      <c r="AD24" s="11" t="n">
+        <v>735.5</v>
+      </c>
+      <c r="AE24" s="11" t="n">
+        <v>3218</v>
+      </c>
       <c r="AF24" s="11" t="n">
         <v>299</v>
       </c>
@@ -7728,12 +8374,24 @@
       <c r="AK24" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="AL24" s="11" t="n"/>
-      <c r="AM24" s="11" t="n"/>
-      <c r="AN24" s="11" t="n"/>
-      <c r="AO24" s="11" t="n"/>
-      <c r="AP24" s="11" t="n"/>
-      <c r="AQ24" s="11" t="n"/>
+      <c r="AL24" s="11" t="n">
+        <v>1.3669</v>
+      </c>
+      <c r="AM24" s="11" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="AN24" s="11" t="n">
+        <v>106.69</v>
+      </c>
+      <c r="AO24" s="11" t="n">
+        <v>2372</v>
+      </c>
+      <c r="AP24" s="11" t="n">
+        <v>1263</v>
+      </c>
+      <c r="AQ24" s="11" t="n">
+        <v>1817</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
@@ -7801,22 +8459,22 @@
         </is>
       </c>
       <c r="U25" s="14" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="V25" s="14" t="n">
         <v>4.4</v>
       </c>
       <c r="W25" s="14" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="X25" s="14" t="n">
-        <v>1750</v>
+        <v>175</v>
       </c>
       <c r="Y25" s="14" t="n">
-        <v>1555.6</v>
+        <v>155.6</v>
       </c>
       <c r="Z25" s="14" t="n">
-        <v>933333.3</v>
+        <v>933</v>
       </c>
       <c r="AA25" s="14" t="n"/>
       <c r="AB25" s="14" t="n">
@@ -7825,8 +8483,12 @@
       <c r="AC25" s="14" t="n">
         <v>553</v>
       </c>
-      <c r="AD25" s="14" t="n"/>
-      <c r="AE25" s="14" t="n"/>
+      <c r="AD25" s="14" t="n">
+        <v>813.5</v>
+      </c>
+      <c r="AE25" s="14" t="n">
+        <v>3660</v>
+      </c>
       <c r="AF25" s="14" t="n">
         <v>340</v>
       </c>
@@ -7845,12 +8507,24 @@
       <c r="AK25" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="AL25" s="14" t="n"/>
-      <c r="AM25" s="14" t="n"/>
-      <c r="AN25" s="14" t="n"/>
-      <c r="AO25" s="14" t="n"/>
-      <c r="AP25" s="14" t="n"/>
-      <c r="AQ25" s="14" t="n"/>
+      <c r="AL25" s="14" t="n">
+        <v>1.4551</v>
+      </c>
+      <c r="AM25" s="14" t="n">
+        <v>237.73</v>
+      </c>
+      <c r="AN25" s="14" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="AO25" s="14" t="n">
+        <v>2654</v>
+      </c>
+      <c r="AP25" s="14" t="n">
+        <v>1366</v>
+      </c>
+      <c r="AQ25" s="14" t="n">
+        <v>2010</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -7918,22 +8592,22 @@
         </is>
       </c>
       <c r="U26" s="11" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="V26" s="11" t="n">
         <v>4.8</v>
       </c>
       <c r="W26" s="11" t="n">
-        <v>842.1</v>
+        <v>84.2</v>
       </c>
       <c r="X26" s="11" t="n">
-        <v>2105.3</v>
+        <v>210.5</v>
       </c>
       <c r="Y26" s="11" t="n">
-        <v>1904.8</v>
+        <v>190.5</v>
       </c>
       <c r="Z26" s="11" t="n">
-        <v>1111111.1</v>
+        <v>1111</v>
       </c>
       <c r="AA26" s="11" t="n"/>
       <c r="AB26" s="11" t="n">
@@ -7942,8 +8616,12 @@
       <c r="AC26" s="11" t="n">
         <v>585</v>
       </c>
-      <c r="AD26" s="11" t="n"/>
-      <c r="AE26" s="11" t="n"/>
+      <c r="AD26" s="11" t="n">
+        <v>866</v>
+      </c>
+      <c r="AE26" s="11" t="n">
+        <v>4155</v>
+      </c>
       <c r="AF26" s="11" t="n">
         <v>386</v>
       </c>
@@ -7962,12 +8640,24 @@
       <c r="AK26" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="AL26" s="11" t="n"/>
-      <c r="AM26" s="11" t="n"/>
-      <c r="AN26" s="11" t="n"/>
-      <c r="AO26" s="11" t="n"/>
-      <c r="AP26" s="11" t="n"/>
-      <c r="AQ26" s="11" t="n"/>
+      <c r="AL26" s="11" t="n">
+        <v>1.3448</v>
+      </c>
+      <c r="AM26" s="11" t="n">
+        <v>181.15</v>
+      </c>
+      <c r="AN26" s="11" t="n">
+        <v>76.37</v>
+      </c>
+      <c r="AO26" s="11" t="n">
+        <v>2834</v>
+      </c>
+      <c r="AP26" s="11" t="n">
+        <v>1446</v>
+      </c>
+      <c r="AQ26" s="11" t="n">
+        <v>2140</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
@@ -7997,23 +8687,49 @@
       <c r="I27" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="J27" s="14" t="n"/>
+      <c r="J27" s="14" t="n">
+        <v>775</v>
+      </c>
       <c r="K27" s="14" t="n"/>
-      <c r="L27" s="14" t="n"/>
-      <c r="M27" s="14" t="n"/>
-      <c r="N27" s="14" t="n"/>
-      <c r="O27" s="14" t="n"/>
-      <c r="P27" s="14" t="n"/>
-      <c r="Q27" s="14" t="n"/>
+      <c r="L27" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>155</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P27" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="R27" s="14" t="n"/>
       <c r="S27" s="14" t="n"/>
       <c r="T27" s="14" t="n"/>
-      <c r="U27" s="14" t="n"/>
-      <c r="V27" s="14" t="n"/>
-      <c r="W27" s="14" t="n"/>
-      <c r="X27" s="14" t="n"/>
-      <c r="Y27" s="14" t="n"/>
-      <c r="Z27" s="14" t="n"/>
+      <c r="U27" s="14" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="V27" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="W27" s="14" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="X27" s="14" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="Y27" s="14" t="n">
+        <v>193.8</v>
+      </c>
+      <c r="Z27" s="14" t="n">
+        <v>1123</v>
+      </c>
       <c r="AA27" s="14" t="n"/>
       <c r="AB27" s="14" t="n">
         <v>1170</v>
@@ -8021,8 +8737,12 @@
       <c r="AC27" s="14" t="n">
         <v>590</v>
       </c>
-      <c r="AD27" s="14" t="n"/>
-      <c r="AE27" s="14" t="n"/>
+      <c r="AD27" s="14" t="n">
+        <v>880</v>
+      </c>
+      <c r="AE27" s="14" t="n">
+        <v>4844</v>
+      </c>
       <c r="AF27" s="14" t="n">
         <v>450</v>
       </c>
@@ -8041,12 +8761,24 @@
       <c r="AK27" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="AL27" s="14" t="n"/>
-      <c r="AM27" s="14" t="n"/>
-      <c r="AN27" s="14" t="n"/>
-      <c r="AO27" s="14" t="n"/>
-      <c r="AP27" s="14" t="n"/>
-      <c r="AQ27" s="14" t="n"/>
+      <c r="AL27" s="14" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="AM27" s="14" t="n">
+        <v>170.12</v>
+      </c>
+      <c r="AN27" s="14" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="AO27" s="14" t="n">
+        <v>2891</v>
+      </c>
+      <c r="AP27" s="14" t="n">
+        <v>1458</v>
+      </c>
+      <c r="AQ27" s="14" t="n">
+        <v>2175</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
@@ -8114,22 +8846,22 @@
         </is>
       </c>
       <c r="U28" s="11" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="V28" s="11" t="n">
         <v>5.2</v>
       </c>
       <c r="W28" s="11" t="n">
-        <v>882.4</v>
+        <v>88.2</v>
       </c>
       <c r="X28" s="11" t="n">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="Y28" s="11" t="n">
-        <v>1973.7</v>
+        <v>197.4</v>
       </c>
       <c r="Z28" s="11" t="n">
-        <v>1153846.2</v>
+        <v>1154</v>
       </c>
       <c r="AA28" s="11" t="n"/>
       <c r="AB28" s="11" t="n">
@@ -8138,8 +8870,12 @@
       <c r="AC28" s="11" t="n">
         <v>601</v>
       </c>
-      <c r="AD28" s="11" t="n"/>
-      <c r="AE28" s="11" t="n"/>
+      <c r="AD28" s="11" t="n">
+        <v>896.5</v>
+      </c>
+      <c r="AE28" s="11" t="n">
+        <v>5845</v>
+      </c>
       <c r="AF28" s="11" t="n">
         <v>543</v>
       </c>
@@ -8158,12 +8894,24 @@
       <c r="AK28" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="AL28" s="11" t="n"/>
-      <c r="AM28" s="11" t="n"/>
-      <c r="AN28" s="11" t="n"/>
-      <c r="AO28" s="11" t="n"/>
-      <c r="AP28" s="11" t="n"/>
-      <c r="AQ28" s="11" t="n"/>
+      <c r="AL28" s="11" t="n">
+        <v>1.4992</v>
+      </c>
+      <c r="AM28" s="11" t="n">
+        <v>166.82</v>
+      </c>
+      <c r="AN28" s="11" t="n">
+        <v>73.22</v>
+      </c>
+      <c r="AO28" s="11" t="n">
+        <v>2945</v>
+      </c>
+      <c r="AP28" s="11" t="n">
+        <v>1485</v>
+      </c>
+      <c r="AQ28" s="11" t="n">
+        <v>2215</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
@@ -8231,22 +8979,22 @@
         </is>
       </c>
       <c r="U29" s="14" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="V29" s="14" t="n">
         <v>5.5</v>
       </c>
       <c r="W29" s="14" t="n">
-        <v>857.1</v>
+        <v>85.7</v>
       </c>
       <c r="X29" s="14" t="n">
-        <v>2400</v>
+        <v>240</v>
       </c>
       <c r="Y29" s="14" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="Z29" s="14" t="n">
-        <v>1090909.1</v>
+        <v>1091</v>
       </c>
       <c r="AA29" s="14" t="n"/>
       <c r="AB29" s="14" t="n">
@@ -8255,8 +9003,12 @@
       <c r="AC29" s="14" t="n">
         <v>630</v>
       </c>
-      <c r="AD29" s="14" t="n"/>
-      <c r="AE29" s="14" t="n"/>
+      <c r="AD29" s="14" t="n">
+        <v>933</v>
+      </c>
+      <c r="AE29" s="14" t="n">
+        <v>6717</v>
+      </c>
       <c r="AF29" s="14" t="n">
         <v>624</v>
       </c>
@@ -8275,12 +9027,24 @@
       <c r="AK29" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="AL29" s="14" t="n"/>
-      <c r="AM29" s="14" t="n"/>
-      <c r="AN29" s="14" t="n"/>
-      <c r="AO29" s="14" t="n"/>
-      <c r="AP29" s="14" t="n"/>
-      <c r="AQ29" s="14" t="n"/>
+      <c r="AL29" s="14" t="n">
+        <v>1.5873</v>
+      </c>
+      <c r="AM29" s="14" t="n">
+        <v>158</v>
+      </c>
+      <c r="AN29" s="14" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="AO29" s="14" t="n">
+        <v>3054</v>
+      </c>
+      <c r="AP29" s="14" t="n">
+        <v>1557</v>
+      </c>
+      <c r="AQ29" s="14" t="n">
+        <v>2305</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
@@ -8348,22 +9112,22 @@
         </is>
       </c>
       <c r="U30" s="11" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="V30" s="11" t="n">
         <v>5</v>
       </c>
       <c r="W30" s="11" t="n">
-        <v>750</v>
+        <v>75</v>
       </c>
       <c r="X30" s="11" t="n">
-        <v>2250</v>
+        <v>225</v>
       </c>
       <c r="Y30" s="11" t="n">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="Z30" s="11" t="n">
-        <v>1071428.6</v>
+        <v>1071</v>
       </c>
       <c r="AA30" s="11" t="n"/>
       <c r="AB30" s="11" t="n">
@@ -8372,8 +9136,12 @@
       <c r="AC30" s="11" t="n">
         <v>658</v>
       </c>
-      <c r="AD30" s="11" t="n"/>
-      <c r="AE30" s="11" t="n"/>
+      <c r="AD30" s="11" t="n">
+        <v>974</v>
+      </c>
+      <c r="AE30" s="11" t="n">
+        <v>6792</v>
+      </c>
       <c r="AF30" s="11" t="n">
         <v>631</v>
       </c>
@@ -8392,12 +9160,24 @@
       <c r="AK30" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="AL30" s="11" t="n"/>
-      <c r="AM30" s="11" t="n"/>
-      <c r="AN30" s="11" t="n"/>
-      <c r="AO30" s="11" t="n"/>
-      <c r="AP30" s="11" t="n"/>
-      <c r="AQ30" s="11" t="n"/>
+      <c r="AL30" s="11" t="n">
+        <v>1.4771</v>
+      </c>
+      <c r="AM30" s="11" t="n">
+        <v>203.19</v>
+      </c>
+      <c r="AN30" s="11" t="n">
+        <v>91.33</v>
+      </c>
+      <c r="AO30" s="11" t="n">
+        <v>3188</v>
+      </c>
+      <c r="AP30" s="11" t="n">
+        <v>1626</v>
+      </c>
+      <c r="AQ30" s="11" t="n">
+        <v>2407</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
@@ -8465,22 +9245,22 @@
         </is>
       </c>
       <c r="U31" s="14" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="V31" s="14" t="n">
         <v>6</v>
       </c>
       <c r="W31" s="14" t="n">
-        <v>666.7</v>
+        <v>66.7</v>
       </c>
       <c r="X31" s="14" t="n">
-        <v>2142.9</v>
+        <v>214.3</v>
       </c>
       <c r="Y31" s="14" t="n">
-        <v>1714.3</v>
+        <v>171.4</v>
       </c>
       <c r="Z31" s="14" t="n">
-        <v>1200000</v>
+        <v>1200</v>
       </c>
       <c r="AA31" s="14" t="n"/>
       <c r="AB31" s="14" t="n">
@@ -8489,8 +9269,12 @@
       <c r="AC31" s="14" t="n">
         <v>695</v>
       </c>
-      <c r="AD31" s="14" t="n"/>
-      <c r="AE31" s="14" t="n"/>
+      <c r="AD31" s="14" t="n">
+        <v>1036.5</v>
+      </c>
+      <c r="AE31" s="14" t="n">
+        <v>7406</v>
+      </c>
       <c r="AF31" s="14" t="n">
         <v>688</v>
       </c>
@@ -8509,12 +9293,24 @@
       <c r="AK31" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="AL31" s="14" t="n"/>
-      <c r="AM31" s="14" t="n"/>
-      <c r="AN31" s="14" t="n"/>
-      <c r="AO31" s="14" t="n"/>
-      <c r="AP31" s="14" t="n"/>
-      <c r="AQ31" s="14" t="n"/>
+      <c r="AL31" s="14" t="n">
+        <v>1.8078</v>
+      </c>
+      <c r="AM31" s="14" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="AN31" s="14" t="n">
+        <v>95.27</v>
+      </c>
+      <c r="AO31" s="14" t="n">
+        <v>3405</v>
+      </c>
+      <c r="AP31" s="14" t="n">
+        <v>1717</v>
+      </c>
+      <c r="AQ31" s="14" t="n">
+        <v>2561</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -8544,23 +9340,49 @@
       <c r="I32" s="11" t="n">
         <v>2900</v>
       </c>
-      <c r="J32" s="11" t="n"/>
+      <c r="J32" s="11" t="n">
+        <v>750</v>
+      </c>
       <c r="K32" s="11" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="11" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="11" t="n"/>
+      <c r="L32" s="11" t="n">
+        <v>775</v>
+      </c>
+      <c r="M32" s="11" t="n">
+        <v>115</v>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="O32" s="11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P32" s="11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q32" s="11" t="n">
+        <v>0.57</v>
+      </c>
       <c r="R32" s="11" t="n"/>
       <c r="S32" s="11" t="n"/>
       <c r="T32" s="11" t="n"/>
-      <c r="U32" s="11" t="n"/>
-      <c r="V32" s="11" t="n"/>
-      <c r="W32" s="11" t="n"/>
-      <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="11" t="n"/>
-      <c r="Z32" s="11" t="n"/>
+      <c r="U32" s="11" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="V32" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W32" s="11" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="X32" s="11" t="n">
+        <v>238.1</v>
+      </c>
+      <c r="Y32" s="11" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="Z32" s="11" t="n">
+        <v>1316</v>
+      </c>
       <c r="AA32" s="11" t="n"/>
       <c r="AB32" s="11" t="n">
         <v>1540</v>
@@ -8568,8 +9390,12 @@
       <c r="AC32" s="11" t="n">
         <v>757</v>
       </c>
-      <c r="AD32" s="11" t="n"/>
-      <c r="AE32" s="11" t="n"/>
+      <c r="AD32" s="11" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="AE32" s="11" t="n">
+        <v>8374</v>
+      </c>
       <c r="AF32" s="11" t="n">
         <v>778</v>
       </c>
@@ -8588,12 +9414,24 @@
       <c r="AK32" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="AL32" s="11" t="n"/>
-      <c r="AM32" s="11" t="n"/>
-      <c r="AN32" s="11" t="n"/>
-      <c r="AO32" s="11" t="n"/>
-      <c r="AP32" s="11" t="n"/>
-      <c r="AQ32" s="11" t="n"/>
+      <c r="AL32" s="11" t="n">
+        <v>1.8519</v>
+      </c>
+      <c r="AM32" s="11" t="n">
+        <v>210.91</v>
+      </c>
+      <c r="AN32" s="11" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AO32" s="11" t="n">
+        <v>3805</v>
+      </c>
+      <c r="AP32" s="11" t="n">
+        <v>1871</v>
+      </c>
+      <c r="AQ32" s="11" t="n">
+        <v>2838</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n">
@@ -8667,16 +9505,16 @@
         <v>6.9</v>
       </c>
       <c r="W33" s="14" t="n">
-        <v>782.6</v>
+        <v>78.3</v>
       </c>
       <c r="X33" s="14" t="n">
-        <v>2571.4</v>
+        <v>257.1</v>
       </c>
       <c r="Y33" s="14" t="n">
-        <v>2142.9</v>
+        <v>214.3</v>
       </c>
       <c r="Z33" s="14" t="n">
-        <v>1384615.4</v>
+        <v>1385</v>
       </c>
       <c r="AA33" s="14" t="n"/>
       <c r="AB33" s="14" t="n">
@@ -8685,8 +9523,12 @@
       <c r="AC33" s="14" t="n">
         <v>853</v>
       </c>
-      <c r="AD33" s="14" t="n"/>
-      <c r="AE33" s="14" t="n"/>
+      <c r="AD33" s="14" t="n">
+        <v>1295</v>
+      </c>
+      <c r="AE33" s="14" t="n">
+        <v>10344</v>
+      </c>
       <c r="AF33" s="14" t="n">
         <v>961</v>
       </c>
@@ -8705,12 +9547,24 @@
       <c r="AK33" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="AL33" s="14" t="n"/>
-      <c r="AM33" s="14" t="n"/>
-      <c r="AN33" s="14" t="n"/>
-      <c r="AO33" s="14" t="n"/>
-      <c r="AP33" s="14" t="n"/>
-      <c r="AQ33" s="14" t="n"/>
+      <c r="AL33" s="14" t="n">
+        <v>1.9842</v>
+      </c>
+      <c r="AM33" s="14" t="n">
+        <v>207.97</v>
+      </c>
+      <c r="AN33" s="14" t="n">
+        <v>78.73999999999999</v>
+      </c>
+      <c r="AO33" s="14" t="n">
+        <v>4292</v>
+      </c>
+      <c r="AP33" s="14" t="n">
+        <v>2108</v>
+      </c>
+      <c r="AQ33" s="14" t="n">
+        <v>3200</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
@@ -8740,23 +9594,49 @@
       <c r="I34" s="11" t="n">
         <v>3300</v>
       </c>
-      <c r="J34" s="11" t="n"/>
+      <c r="J34" s="11" t="n">
+        <v>1350</v>
+      </c>
       <c r="K34" s="11" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="11" t="n"/>
-      <c r="N34" s="11" t="n"/>
-      <c r="O34" s="11" t="n"/>
-      <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="11" t="n"/>
+      <c r="L34" s="11" t="n">
+        <v>1150</v>
+      </c>
+      <c r="M34" s="11" t="n">
+        <v>155</v>
+      </c>
+      <c r="N34" s="11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O34" s="11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="P34" s="11" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Q34" s="11" t="n">
+        <v>0.73</v>
+      </c>
       <c r="R34" s="11" t="n"/>
       <c r="S34" s="11" t="n"/>
       <c r="T34" s="11" t="n"/>
-      <c r="U34" s="11" t="n"/>
-      <c r="V34" s="11" t="n"/>
-      <c r="W34" s="11" t="n"/>
-      <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="11" t="n"/>
-      <c r="Z34" s="11" t="n"/>
+      <c r="U34" s="11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V34" s="11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W34" s="11" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="X34" s="11" t="n">
+        <v>317.6</v>
+      </c>
+      <c r="Y34" s="11" t="n">
+        <v>252.3</v>
+      </c>
+      <c r="Z34" s="11" t="n">
+        <v>1849</v>
+      </c>
       <c r="AA34" s="11" t="n"/>
       <c r="AB34" s="11" t="n">
         <v>2024</v>
@@ -8764,8 +9644,12 @@
       <c r="AC34" s="11" t="n">
         <v>972</v>
       </c>
-      <c r="AD34" s="11" t="n"/>
-      <c r="AE34" s="11" t="n"/>
+      <c r="AD34" s="11" t="n">
+        <v>1498</v>
+      </c>
+      <c r="AE34" s="11" t="n">
+        <v>11033</v>
+      </c>
       <c r="AF34" s="11" t="n">
         <v>1025</v>
       </c>
@@ -8784,12 +9668,24 @@
       <c r="AK34" s="11" t="n">
         <v>86</v>
       </c>
-      <c r="AL34" s="11" t="n"/>
-      <c r="AM34" s="11" t="n"/>
-      <c r="AN34" s="11" t="n"/>
-      <c r="AO34" s="11" t="n"/>
-      <c r="AP34" s="11" t="n"/>
-      <c r="AQ34" s="11" t="n"/>
+      <c r="AL34" s="11" t="n">
+        <v>1.896</v>
+      </c>
+      <c r="AM34" s="11" t="n">
+        <v>236.26</v>
+      </c>
+      <c r="AN34" s="11" t="n">
+        <v>119.68</v>
+      </c>
+      <c r="AO34" s="11" t="n">
+        <v>5001</v>
+      </c>
+      <c r="AP34" s="11" t="n">
+        <v>2402</v>
+      </c>
+      <c r="AQ34" s="11" t="n">
+        <v>3702</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n">
@@ -8859,22 +9755,22 @@
         </is>
       </c>
       <c r="U35" s="14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V35" s="14" t="n">
         <v>10</v>
       </c>
       <c r="W35" s="14" t="n">
-        <v>1028.6</v>
+        <v>102.9</v>
       </c>
       <c r="X35" s="14" t="n">
-        <v>3600</v>
+        <v>360</v>
       </c>
       <c r="Y35" s="14" t="n">
-        <v>2769.2</v>
+        <v>276.9</v>
       </c>
       <c r="Z35" s="14" t="n">
-        <v>2250000</v>
+        <v>2250</v>
       </c>
       <c r="AA35" s="14" t="n">
         <v>8</v>
@@ -8885,8 +9781,12 @@
       <c r="AC35" s="14" t="n">
         <v>1197</v>
       </c>
-      <c r="AD35" s="14" t="n"/>
-      <c r="AE35" s="14" t="n"/>
+      <c r="AD35" s="14" t="n">
+        <v>1887.5</v>
+      </c>
+      <c r="AE35" s="14" t="n">
+        <v>11830</v>
+      </c>
       <c r="AF35" s="14" t="n">
         <v>1099</v>
       </c>
@@ -8905,12 +9805,24 @@
       <c r="AK35" s="14" t="n">
         <v>91</v>
       </c>
-      <c r="AL35" s="14" t="n"/>
-      <c r="AM35" s="14" t="n"/>
-      <c r="AN35" s="14" t="n"/>
-      <c r="AO35" s="14" t="n"/>
-      <c r="AP35" s="14" t="n"/>
-      <c r="AQ35" s="14" t="n"/>
+      <c r="AL35" s="14" t="n">
+        <v>2.0062</v>
+      </c>
+      <c r="AM35" s="14" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="AN35" s="14" t="n">
+        <v>165.35</v>
+      </c>
+      <c r="AO35" s="14" t="n">
+        <v>6370</v>
+      </c>
+      <c r="AP35" s="14" t="n">
+        <v>2958</v>
+      </c>
+      <c r="AQ35" s="14" t="n">
+        <v>4664</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
@@ -8980,22 +9892,22 @@
         </is>
       </c>
       <c r="U36" s="11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V36" s="11" t="n">
         <v>11.9</v>
       </c>
       <c r="W36" s="11" t="n">
-        <v>1136.4</v>
+        <v>113.6</v>
       </c>
       <c r="X36" s="11" t="n">
-        <v>3125</v>
+        <v>312.5</v>
       </c>
       <c r="Y36" s="11" t="n">
-        <v>2777.8</v>
+        <v>277.8</v>
       </c>
       <c r="Z36" s="11" t="n">
-        <v>2777777.8</v>
+        <v>2778</v>
       </c>
       <c r="AA36" s="11" t="n">
         <v>10</v>
@@ -9006,8 +9918,12 @@
       <c r="AC36" s="11" t="n">
         <v>1500</v>
       </c>
-      <c r="AD36" s="11" t="n"/>
-      <c r="AE36" s="11" t="n"/>
+      <c r="AD36" s="11" t="n">
+        <v>2349.5</v>
+      </c>
+      <c r="AE36" s="11" t="n">
+        <v>13143</v>
+      </c>
       <c r="AF36" s="11" t="n">
         <v>1221</v>
       </c>
@@ -9026,12 +9942,24 @@
       <c r="AK36" s="11" t="n">
         <v>101</v>
       </c>
-      <c r="AL36" s="11" t="n"/>
-      <c r="AM36" s="11" t="n"/>
-      <c r="AN36" s="11" t="n"/>
-      <c r="AO36" s="11" t="n"/>
-      <c r="AP36" s="11" t="n"/>
-      <c r="AQ36" s="11" t="n"/>
+      <c r="AL36" s="11" t="n">
+        <v>2.2267</v>
+      </c>
+      <c r="AM36" s="11" t="n">
+        <v>371.48</v>
+      </c>
+      <c r="AN36" s="11" t="n">
+        <v>159.83</v>
+      </c>
+      <c r="AO36" s="11" t="n">
+        <v>7905</v>
+      </c>
+      <c r="AP36" s="11" t="n">
+        <v>3707</v>
+      </c>
+      <c r="AQ36" s="11" t="n">
+        <v>5806</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n">
@@ -9101,22 +10029,22 @@
         </is>
       </c>
       <c r="U37" s="14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V37" s="14" t="n">
         <v>10</v>
       </c>
       <c r="W37" s="14" t="n">
-        <v>1428.6</v>
+        <v>142.9</v>
       </c>
       <c r="X37" s="14" t="n">
-        <v>4444.4</v>
+        <v>444.4</v>
       </c>
       <c r="Y37" s="14" t="n">
-        <v>3636.4</v>
+        <v>363.6</v>
       </c>
       <c r="Z37" s="14" t="n">
-        <v>2666666.7</v>
+        <v>2667</v>
       </c>
       <c r="AA37" s="14" t="n">
         <v>9</v>
@@ -9127,8 +10055,12 @@
       <c r="AC37" s="14" t="n">
         <v>1568</v>
       </c>
-      <c r="AD37" s="14" t="n"/>
-      <c r="AE37" s="14" t="n"/>
+      <c r="AD37" s="14" t="n">
+        <v>2460</v>
+      </c>
+      <c r="AE37" s="14" t="n">
+        <v>12002</v>
+      </c>
       <c r="AF37" s="14" t="n">
         <v>1115</v>
       </c>
@@ -9147,12 +10079,24 @@
       <c r="AK37" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="AL37" s="14" t="n"/>
-      <c r="AM37" s="14" t="n"/>
-      <c r="AN37" s="14" t="n"/>
-      <c r="AO37" s="14" t="n"/>
-      <c r="AP37" s="14" t="n"/>
-      <c r="AQ37" s="14" t="n"/>
+      <c r="AL37" s="14" t="n">
+        <v>1.8519</v>
+      </c>
+      <c r="AM37" s="14" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="AN37" s="14" t="n">
+        <v>139.76</v>
+      </c>
+      <c r="AO37" s="14" t="n">
+        <v>8283</v>
+      </c>
+      <c r="AP37" s="14" t="n">
+        <v>3875</v>
+      </c>
+      <c r="AQ37" s="14" t="n">
+        <v>6079</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
@@ -9222,22 +10166,22 @@
         </is>
       </c>
       <c r="U38" s="11" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V38" s="11" t="n">
         <v>12.2</v>
       </c>
       <c r="W38" s="11" t="n">
-        <v>1435.9</v>
+        <v>143.6</v>
       </c>
       <c r="X38" s="11" t="n">
-        <v>4666.7</v>
+        <v>466.7</v>
       </c>
       <c r="Y38" s="11" t="n">
-        <v>4117.6</v>
+        <v>411.8</v>
       </c>
       <c r="Z38" s="11" t="n">
-        <v>2800000</v>
+        <v>2800</v>
       </c>
       <c r="AA38" s="11" t="n">
         <v>11</v>
@@ -9248,8 +10192,12 @@
       <c r="AC38" s="11" t="n">
         <v>1800</v>
       </c>
-      <c r="AD38" s="11" t="n"/>
-      <c r="AE38" s="11" t="n"/>
+      <c r="AD38" s="11" t="n">
+        <v>2805</v>
+      </c>
+      <c r="AE38" s="11" t="n">
+        <v>12551</v>
+      </c>
       <c r="AF38" s="11" t="n">
         <v>1166</v>
       </c>
@@ -9268,12 +10216,24 @@
       <c r="AK38" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="AL38" s="11" t="n"/>
-      <c r="AM38" s="11" t="n"/>
-      <c r="AN38" s="11" t="n"/>
-      <c r="AO38" s="11" t="n"/>
-      <c r="AP38" s="11" t="n"/>
-      <c r="AQ38" s="11" t="n"/>
+      <c r="AL38" s="11" t="n">
+        <v>2.0724</v>
+      </c>
+      <c r="AM38" s="11" t="n">
+        <v>415.21</v>
+      </c>
+      <c r="AN38" s="11" t="n">
+        <v>203.93</v>
+      </c>
+      <c r="AO38" s="11" t="n">
+        <v>9415</v>
+      </c>
+      <c r="AP38" s="11" t="n">
+        <v>4448</v>
+      </c>
+      <c r="AQ38" s="11" t="n">
+        <v>6931</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n">
@@ -9343,22 +10303,22 @@
         </is>
       </c>
       <c r="U39" s="14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V39" s="14" t="n">
         <v>12.5</v>
       </c>
       <c r="W39" s="14" t="n">
-        <v>1750</v>
+        <v>175</v>
       </c>
       <c r="X39" s="14" t="n">
-        <v>5645.2</v>
+        <v>564.5</v>
       </c>
       <c r="Y39" s="14" t="n">
-        <v>4861.1</v>
+        <v>486.1</v>
       </c>
       <c r="Z39" s="14" t="n">
-        <v>3181818.2</v>
+        <v>3182</v>
       </c>
       <c r="AA39" s="14" t="n">
         <v>13</v>
@@ -9369,8 +10329,12 @@
       <c r="AC39" s="14" t="n">
         <v>2200</v>
       </c>
-      <c r="AD39" s="14" t="n"/>
-      <c r="AE39" s="14" t="n"/>
+      <c r="AD39" s="14" t="n">
+        <v>3445</v>
+      </c>
+      <c r="AE39" s="14" t="n">
+        <v>12809</v>
+      </c>
       <c r="AF39" s="14" t="n">
         <v>1190</v>
       </c>
@@ -9389,12 +10353,24 @@
       <c r="AK39" s="14" t="n">
         <v>111</v>
       </c>
-      <c r="AL39" s="14" t="n"/>
-      <c r="AM39" s="14" t="n"/>
-      <c r="AN39" s="14" t="n"/>
-      <c r="AO39" s="14" t="n"/>
-      <c r="AP39" s="14" t="n"/>
-      <c r="AQ39" s="14" t="n"/>
+      <c r="AL39" s="14" t="n">
+        <v>2.4471</v>
+      </c>
+      <c r="AM39" s="14" t="n">
+        <v>454.52</v>
+      </c>
+      <c r="AN39" s="14" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="AO39" s="14" t="n">
+        <v>11589</v>
+      </c>
+      <c r="AP39" s="14" t="n">
+        <v>5436</v>
+      </c>
+      <c r="AQ39" s="14" t="n">
+        <v>8513</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
@@ -9464,22 +10440,22 @@
         </is>
       </c>
       <c r="U40" s="11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V40" s="11" t="n">
         <v>12.2</v>
       </c>
       <c r="W40" s="11" t="n">
-        <v>1783.8</v>
+        <v>178.4</v>
       </c>
       <c r="X40" s="11" t="n">
-        <v>5689.7</v>
+        <v>569</v>
       </c>
       <c r="Y40" s="11" t="n">
-        <v>4714.3</v>
+        <v>471.4</v>
       </c>
       <c r="Z40" s="11" t="n">
-        <v>3142857.1</v>
+        <v>3143</v>
       </c>
       <c r="AA40" s="11" t="n">
         <v>12</v>
@@ -9490,8 +10466,12 @@
       <c r="AC40" s="11" t="n">
         <v>2700</v>
       </c>
-      <c r="AD40" s="11" t="n"/>
-      <c r="AE40" s="11" t="n"/>
+      <c r="AD40" s="11" t="n">
+        <v>4215.5</v>
+      </c>
+      <c r="AE40" s="11" t="n">
+        <v>13153</v>
+      </c>
       <c r="AF40" s="11" t="n">
         <v>1222</v>
       </c>
@@ -9510,12 +10490,24 @@
       <c r="AK40" s="11" t="n">
         <v>118</v>
       </c>
-      <c r="AL40" s="11" t="n"/>
-      <c r="AM40" s="11" t="n"/>
-      <c r="AN40" s="11" t="n"/>
-      <c r="AO40" s="11" t="n"/>
-      <c r="AP40" s="11" t="n"/>
-      <c r="AQ40" s="11" t="n"/>
+      <c r="AL40" s="11" t="n">
+        <v>2.6015</v>
+      </c>
+      <c r="AM40" s="11" t="n">
+        <v>529.11</v>
+      </c>
+      <c r="AN40" s="11" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="AO40" s="11" t="n">
+        <v>14162</v>
+      </c>
+      <c r="AP40" s="11" t="n">
+        <v>6672</v>
+      </c>
+      <c r="AQ40" s="11" t="n">
+        <v>10417</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n">
@@ -9591,16 +10583,16 @@
         <v>11.5</v>
       </c>
       <c r="W41" s="14" t="n">
-        <v>1764.7</v>
+        <v>176.5</v>
       </c>
       <c r="X41" s="14" t="n">
-        <v>5454.5</v>
+        <v>545.5</v>
       </c>
       <c r="Y41" s="14" t="n">
-        <v>4615.4</v>
+        <v>461.5</v>
       </c>
       <c r="Z41" s="14" t="n">
-        <v>3157894.7</v>
+        <v>3158</v>
       </c>
       <c r="AA41" s="14" t="n">
         <v>11</v>
@@ -9611,8 +10603,12 @@
       <c r="AC41" s="14" t="n">
         <v>3215</v>
       </c>
-      <c r="AD41" s="14" t="n"/>
-      <c r="AE41" s="14" t="n"/>
+      <c r="AD41" s="14" t="n">
+        <v>5199</v>
+      </c>
+      <c r="AE41" s="14" t="n">
+        <v>14176</v>
+      </c>
       <c r="AF41" s="14" t="n">
         <v>1317</v>
       </c>
@@ -9631,12 +10627,24 @@
       <c r="AK41" s="14" t="n">
         <v>126</v>
       </c>
-      <c r="AL41" s="14" t="n"/>
-      <c r="AM41" s="14" t="n"/>
-      <c r="AN41" s="14" t="n"/>
-      <c r="AO41" s="14" t="n"/>
-      <c r="AP41" s="14" t="n"/>
-      <c r="AQ41" s="14" t="n"/>
+      <c r="AL41" s="14" t="n">
+        <v>2.7778</v>
+      </c>
+      <c r="AM41" s="14" t="n">
+        <v>477.67</v>
+      </c>
+      <c r="AN41" s="14" t="n">
+        <v>175.58</v>
+      </c>
+      <c r="AO41" s="14" t="n">
+        <v>17750</v>
+      </c>
+      <c r="AP41" s="14" t="n">
+        <v>7944</v>
+      </c>
+      <c r="AQ41" s="14" t="n">
+        <v>12847</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
@@ -9706,22 +10714,22 @@
         </is>
       </c>
       <c r="U42" s="11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V42" s="11" t="n">
         <v>10.8</v>
       </c>
       <c r="W42" s="11" t="n">
-        <v>1793.1</v>
+        <v>179.3</v>
       </c>
       <c r="X42" s="11" t="n">
-        <v>5416.7</v>
+        <v>541.7</v>
       </c>
       <c r="Y42" s="11" t="n">
-        <v>4482.8</v>
+        <v>448.3</v>
       </c>
       <c r="Z42" s="11" t="n">
-        <v>2888888.9</v>
+        <v>2889</v>
       </c>
       <c r="AA42" s="11" t="n">
         <v>10</v>
@@ -9732,8 +10740,12 @@
       <c r="AC42" s="11" t="n">
         <v>3530</v>
       </c>
-      <c r="AD42" s="11" t="n"/>
-      <c r="AE42" s="11" t="n"/>
+      <c r="AD42" s="11" t="n">
+        <v>5734.5</v>
+      </c>
+      <c r="AE42" s="11" t="n">
+        <v>16867</v>
+      </c>
       <c r="AF42" s="11" t="n">
         <v>1567</v>
       </c>
@@ -9752,12 +10764,24 @@
       <c r="AK42" s="11" t="n">
         <v>148</v>
       </c>
-      <c r="AL42" s="11" t="n"/>
-      <c r="AM42" s="11" t="n"/>
-      <c r="AN42" s="11" t="n"/>
-      <c r="AO42" s="11" t="n"/>
-      <c r="AP42" s="11" t="n"/>
-      <c r="AQ42" s="11" t="n"/>
+      <c r="AL42" s="11" t="n">
+        <v>3.2629</v>
+      </c>
+      <c r="AM42" s="11" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="AN42" s="11" t="n">
+        <v>145.66</v>
+      </c>
+      <c r="AO42" s="11" t="n">
+        <v>19618</v>
+      </c>
+      <c r="AP42" s="11" t="n">
+        <v>8723</v>
+      </c>
+      <c r="AQ42" s="11" t="n">
+        <v>14170</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n">
@@ -9827,22 +10851,22 @@
         </is>
       </c>
       <c r="U43" s="14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V43" s="14" t="n">
         <v>10.9</v>
       </c>
       <c r="W43" s="14" t="n">
-        <v>1920</v>
+        <v>192</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>5714.3</v>
+        <v>571.4</v>
       </c>
       <c r="Y43" s="14" t="n">
-        <v>4363.6</v>
+        <v>436.4</v>
       </c>
       <c r="Z43" s="14" t="n">
-        <v>2823529.4</v>
+        <v>2824</v>
       </c>
       <c r="AA43" s="14" t="n">
         <v>9</v>
@@ -9853,8 +10877,12 @@
       <c r="AC43" s="14" t="n">
         <v>3415</v>
       </c>
-      <c r="AD43" s="14" t="n"/>
-      <c r="AE43" s="14" t="n"/>
+      <c r="AD43" s="14" t="n">
+        <v>5524</v>
+      </c>
+      <c r="AE43" s="14" t="n">
+        <v>17900</v>
+      </c>
       <c r="AF43" s="14" t="n">
         <v>1663</v>
       </c>
@@ -9873,12 +10901,24 @@
       <c r="AK43" s="14" t="n">
         <v>148</v>
       </c>
-      <c r="AL43" s="14" t="n"/>
-      <c r="AM43" s="14" t="n"/>
-      <c r="AN43" s="14" t="n"/>
-      <c r="AO43" s="14" t="n"/>
-      <c r="AP43" s="14" t="n"/>
-      <c r="AQ43" s="14" t="n"/>
+      <c r="AL43" s="14" t="n">
+        <v>3.2629</v>
+      </c>
+      <c r="AM43" s="14" t="n">
+        <v>328.86</v>
+      </c>
+      <c r="AN43" s="14" t="n">
+        <v>142.12</v>
+      </c>
+      <c r="AO43" s="14" t="n">
+        <v>18862</v>
+      </c>
+      <c r="AP43" s="14" t="n">
+        <v>8439</v>
+      </c>
+      <c r="AQ43" s="14" t="n">
+        <v>13650</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n">
@@ -9948,22 +10988,22 @@
         </is>
       </c>
       <c r="U44" s="11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V44" s="11" t="n">
         <v>10.9</v>
       </c>
       <c r="W44" s="11" t="n">
-        <v>2083.3</v>
+        <v>208.3</v>
       </c>
       <c r="X44" s="11" t="n">
-        <v>6250</v>
+        <v>625</v>
       </c>
       <c r="Y44" s="11" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="Z44" s="11" t="n">
-        <v>2840909.1</v>
+        <v>2841</v>
       </c>
       <c r="AA44" s="11" t="n">
         <v>9</v>
@@ -9974,8 +11014,12 @@
       <c r="AC44" s="11" t="n">
         <v>3233</v>
       </c>
-      <c r="AD44" s="11" t="n"/>
-      <c r="AE44" s="11" t="n"/>
+      <c r="AD44" s="11" t="n">
+        <v>5208</v>
+      </c>
+      <c r="AE44" s="11" t="n">
+        <v>18083</v>
+      </c>
       <c r="AF44" s="11" t="n">
         <v>1680</v>
       </c>
@@ -9994,12 +11038,24 @@
       <c r="AK44" s="11" t="n">
         <v>118</v>
       </c>
-      <c r="AL44" s="11" t="n"/>
-      <c r="AM44" s="11" t="n"/>
-      <c r="AN44" s="11" t="n"/>
-      <c r="AO44" s="11" t="n"/>
-      <c r="AP44" s="11" t="n"/>
-      <c r="AQ44" s="11" t="n"/>
+      <c r="AL44" s="11" t="n">
+        <v>2.6015</v>
+      </c>
+      <c r="AM44" s="11" t="n">
+        <v>347.97</v>
+      </c>
+      <c r="AN44" s="11" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="AO44" s="11" t="n">
+        <v>17750</v>
+      </c>
+      <c r="AP44" s="11" t="n">
+        <v>7989</v>
+      </c>
+      <c r="AQ44" s="11" t="n">
+        <v>12869</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n">
@@ -10069,22 +11125,22 @@
         </is>
       </c>
       <c r="U45" s="14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V45" s="14" t="n">
         <v>10</v>
       </c>
       <c r="W45" s="14" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="X45" s="14" t="n">
-        <v>6279.1</v>
+        <v>627.9</v>
       </c>
       <c r="Y45" s="14" t="n">
-        <v>4909.1</v>
+        <v>490.9</v>
       </c>
       <c r="Z45" s="14" t="n">
-        <v>3000000</v>
+        <v>3000</v>
       </c>
       <c r="AA45" s="14" t="n">
         <v>10</v>
@@ -10095,8 +11151,12 @@
       <c r="AC45" s="14" t="n">
         <v>3200</v>
       </c>
-      <c r="AD45" s="14" t="n"/>
-      <c r="AE45" s="14" t="n"/>
+      <c r="AD45" s="14" t="n">
+        <v>5191.5</v>
+      </c>
+      <c r="AE45" s="14" t="n">
+        <v>18406</v>
+      </c>
       <c r="AF45" s="14" t="n">
         <v>1710</v>
       </c>
@@ -10115,12 +11175,24 @@
       <c r="AK45" s="14" t="n">
         <v>118</v>
       </c>
-      <c r="AL45" s="14" t="n"/>
-      <c r="AM45" s="14" t="n"/>
-      <c r="AN45" s="14" t="n"/>
-      <c r="AO45" s="14" t="n"/>
-      <c r="AP45" s="14" t="n"/>
-      <c r="AQ45" s="14" t="n"/>
+      <c r="AL45" s="14" t="n">
+        <v>2.6015</v>
+      </c>
+      <c r="AM45" s="14" t="n">
+        <v>342.82</v>
+      </c>
+      <c r="AN45" s="14" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="AO45" s="14" t="n">
+        <v>17750</v>
+      </c>
+      <c r="AP45" s="14" t="n">
+        <v>7907</v>
+      </c>
+      <c r="AQ45" s="14" t="n">
+        <v>12828</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
@@ -10190,22 +11262,22 @@
         </is>
       </c>
       <c r="U46" s="11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="V46" s="11" t="n">
         <v>8.6</v>
       </c>
       <c r="W46" s="11" t="n">
-        <v>2173.9</v>
+        <v>217.4</v>
       </c>
       <c r="X46" s="11" t="n">
-        <v>6578.9</v>
+        <v>657.9</v>
       </c>
       <c r="Y46" s="11" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="Z46" s="11" t="n">
-        <v>3125000</v>
+        <v>3125</v>
       </c>
       <c r="AA46" s="11" t="n">
         <v>9</v>
@@ -10216,8 +11288,12 @@
       <c r="AC46" s="11" t="n">
         <v>3290</v>
       </c>
-      <c r="AD46" s="11" t="n"/>
-      <c r="AE46" s="11" t="n"/>
+      <c r="AD46" s="11" t="n">
+        <v>5277</v>
+      </c>
+      <c r="AE46" s="11" t="n">
+        <v>18514</v>
+      </c>
       <c r="AF46" s="11" t="n">
         <v>1720</v>
       </c>
@@ -10236,12 +11312,24 @@
       <c r="AK46" s="11" t="n">
         <v>116</v>
       </c>
-      <c r="AL46" s="11" t="n"/>
-      <c r="AM46" s="11" t="n"/>
-      <c r="AN46" s="11" t="n"/>
-      <c r="AO46" s="11" t="n"/>
-      <c r="AP46" s="11" t="n"/>
-      <c r="AQ46" s="11" t="n"/>
+      <c r="AL46" s="11" t="n">
+        <v>2.5574</v>
+      </c>
+      <c r="AM46" s="11" t="n">
+        <v>311.59</v>
+      </c>
+      <c r="AN46" s="11" t="n">
+        <v>142.12</v>
+      </c>
+      <c r="AO46" s="11" t="n">
+        <v>17950</v>
+      </c>
+      <c r="AP46" s="11" t="n">
+        <v>8130</v>
+      </c>
+      <c r="AQ46" s="11" t="n">
+        <v>13040</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n">
@@ -10317,16 +11405,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="W47" s="14" t="n">
-        <v>2095.2</v>
+        <v>209.5</v>
       </c>
       <c r="X47" s="14" t="n">
-        <v>6285.7</v>
+        <v>628.6</v>
       </c>
       <c r="Y47" s="14" t="n">
-        <v>4583.3</v>
+        <v>458.3</v>
       </c>
       <c r="Z47" s="14" t="n">
-        <v>2933333.3</v>
+        <v>2933</v>
       </c>
       <c r="AA47" s="14" t="n">
         <v>8</v>
@@ -10337,8 +11425,12 @@
       <c r="AC47" s="14" t="n">
         <v>3326</v>
       </c>
-      <c r="AD47" s="14" t="n"/>
-      <c r="AE47" s="14" t="n"/>
+      <c r="AD47" s="14" t="n">
+        <v>5295</v>
+      </c>
+      <c r="AE47" s="14" t="n">
+        <v>18729</v>
+      </c>
       <c r="AF47" s="14" t="n">
         <v>1740</v>
       </c>
@@ -10357,12 +11449,24 @@
       <c r="AK47" s="14" t="n">
         <v>116</v>
       </c>
-      <c r="AL47" s="14" t="n"/>
-      <c r="AM47" s="14" t="n"/>
-      <c r="AN47" s="14" t="n"/>
-      <c r="AO47" s="14" t="n"/>
-      <c r="AP47" s="14" t="n"/>
-      <c r="AQ47" s="14" t="n"/>
+      <c r="AL47" s="14" t="n">
+        <v>2.5574</v>
+      </c>
+      <c r="AM47" s="14" t="n">
+        <v>314.9</v>
+      </c>
+      <c r="AN47" s="14" t="n">
+        <v>140.15</v>
+      </c>
+      <c r="AO47" s="14" t="n">
+        <v>17950</v>
+      </c>
+      <c r="AP47" s="14" t="n">
+        <v>8219</v>
+      </c>
+      <c r="AQ47" s="14" t="n">
+        <v>13084</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n">
@@ -10432,22 +11536,22 @@
         </is>
       </c>
       <c r="U48" s="11" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="V48" s="11" t="n">
         <v>9.5</v>
       </c>
       <c r="W48" s="11" t="n">
-        <v>1448.3</v>
+        <v>144.8</v>
       </c>
       <c r="X48" s="11" t="n">
-        <v>4200</v>
+        <v>420</v>
       </c>
       <c r="Y48" s="11" t="n">
-        <v>3500</v>
+        <v>350</v>
       </c>
       <c r="Z48" s="11" t="n">
-        <v>2100000</v>
+        <v>2100</v>
       </c>
       <c r="AA48" s="11" t="n">
         <v>9</v>
@@ -10458,8 +11562,12 @@
       <c r="AC48" s="11" t="n">
         <v>3330</v>
       </c>
-      <c r="AD48" s="11" t="n"/>
-      <c r="AE48" s="11" t="n"/>
+      <c r="AD48" s="11" t="n">
+        <v>5245</v>
+      </c>
+      <c r="AE48" s="11" t="n">
+        <v>17438</v>
+      </c>
       <c r="AF48" s="11" t="n">
         <v>1620</v>
       </c>
@@ -10478,12 +11586,24 @@
       <c r="AK48" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="AL48" s="11" t="n"/>
-      <c r="AM48" s="11" t="n"/>
-      <c r="AN48" s="11" t="n"/>
-      <c r="AO48" s="11" t="n"/>
-      <c r="AP48" s="11" t="n"/>
-      <c r="AQ48" s="11" t="n"/>
+      <c r="AL48" s="11" t="n">
+        <v>2.4251</v>
+      </c>
+      <c r="AM48" s="11" t="n">
+        <v>396.84</v>
+      </c>
+      <c r="AN48" s="11" t="n">
+        <v>178.34</v>
+      </c>
+      <c r="AO48" s="11" t="n">
+        <v>17693</v>
+      </c>
+      <c r="AP48" s="11" t="n">
+        <v>8229</v>
+      </c>
+      <c r="AQ48" s="11" t="n">
+        <v>12961</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n">
@@ -10553,22 +11673,22 @@
         </is>
       </c>
       <c r="U49" s="14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V49" s="14" t="n">
         <v>10.7</v>
       </c>
       <c r="W49" s="14" t="n">
-        <v>1411.8</v>
+        <v>141.2</v>
       </c>
       <c r="X49" s="14" t="n">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="Y49" s="14" t="n">
-        <v>3428.6</v>
+        <v>342.9</v>
       </c>
       <c r="Z49" s="14" t="n">
-        <v>1500000</v>
+        <v>1500</v>
       </c>
       <c r="AA49" s="14" t="n">
         <v>11</v>
@@ -10579,8 +11699,12 @@
       <c r="AC49" s="14" t="n">
         <v>3561</v>
       </c>
-      <c r="AD49" s="14" t="n"/>
-      <c r="AE49" s="14" t="n"/>
+      <c r="AD49" s="14" t="n">
+        <v>5560.5</v>
+      </c>
+      <c r="AE49" s="14" t="n">
+        <v>18449</v>
+      </c>
       <c r="AF49" s="14" t="n">
         <v>1714</v>
       </c>
@@ -10599,12 +11723,24 @@
       <c r="AK49" s="14" t="n">
         <v>136</v>
       </c>
-      <c r="AL49" s="14" t="n"/>
-      <c r="AM49" s="14" t="n"/>
-      <c r="AN49" s="14" t="n"/>
-      <c r="AO49" s="14" t="n"/>
-      <c r="AP49" s="14" t="n"/>
-      <c r="AQ49" s="14" t="n"/>
+      <c r="AL49" s="14" t="n">
+        <v>2.9983</v>
+      </c>
+      <c r="AM49" s="14" t="n">
+        <v>488.7</v>
+      </c>
+      <c r="AN49" s="14" t="n">
+        <v>214.56</v>
+      </c>
+      <c r="AO49" s="14" t="n">
+        <v>18681</v>
+      </c>
+      <c r="AP49" s="14" t="n">
+        <v>8799</v>
+      </c>
+      <c r="AQ49" s="14" t="n">
+        <v>13740</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n">
@@ -10674,22 +11810,22 @@
         </is>
       </c>
       <c r="U50" s="11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V50" s="11" t="n">
         <v>10.8</v>
       </c>
       <c r="W50" s="11" t="n">
-        <v>1368.4</v>
+        <v>136.8</v>
       </c>
       <c r="X50" s="11" t="n">
-        <v>3714.3</v>
+        <v>371.4</v>
       </c>
       <c r="Y50" s="11" t="n">
-        <v>3058.8</v>
+        <v>305.9</v>
       </c>
       <c r="Z50" s="11" t="n">
-        <v>1444444.4</v>
+        <v>1444</v>
       </c>
       <c r="AA50" s="11" t="n">
         <v>12</v>
@@ -10700,8 +11836,12 @@
       <c r="AC50" s="11" t="n">
         <v>4015</v>
       </c>
-      <c r="AD50" s="11" t="n"/>
-      <c r="AE50" s="11" t="n"/>
+      <c r="AD50" s="11" t="n">
+        <v>6883</v>
+      </c>
+      <c r="AE50" s="11" t="n">
+        <v>20451</v>
+      </c>
       <c r="AF50" s="11" t="n">
         <v>1900</v>
       </c>
@@ -10720,12 +11860,24 @@
       <c r="AK50" s="11" t="n">
         <v>152</v>
       </c>
-      <c r="AL50" s="11" t="n"/>
-      <c r="AM50" s="11" t="n"/>
-      <c r="AN50" s="11" t="n"/>
-      <c r="AO50" s="11" t="n"/>
-      <c r="AP50" s="11" t="n"/>
-      <c r="AQ50" s="11" t="n"/>
+      <c r="AL50" s="11" t="n">
+        <v>3.351</v>
+      </c>
+      <c r="AM50" s="11" t="n">
+        <v>521.76</v>
+      </c>
+      <c r="AN50" s="11" t="n">
+        <v>257.47</v>
+      </c>
+      <c r="AO50" s="11" t="n">
+        <v>24095</v>
+      </c>
+      <c r="AP50" s="11" t="n">
+        <v>9921</v>
+      </c>
+      <c r="AQ50" s="11" t="n">
+        <v>17008</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n">
@@ -10795,22 +11947,22 @@
         </is>
       </c>
       <c r="U51" s="14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V51" s="14" t="n">
         <v>10.8</v>
       </c>
       <c r="W51" s="14" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="X51" s="14" t="n">
-        <v>5090.9</v>
+        <v>509.1</v>
       </c>
       <c r="Y51" s="14" t="n">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="Z51" s="14" t="n">
-        <v>1400000</v>
+        <v>1400</v>
       </c>
       <c r="AA51" s="14" t="n">
         <v>11</v>
@@ -10821,8 +11973,12 @@
       <c r="AC51" s="14" t="n">
         <v>4015</v>
       </c>
-      <c r="AD51" s="14" t="n"/>
-      <c r="AE51" s="14" t="n"/>
+      <c r="AD51" s="14" t="n">
+        <v>7925</v>
+      </c>
+      <c r="AE51" s="14" t="n">
+        <v>22066</v>
+      </c>
       <c r="AF51" s="14" t="n">
         <v>2050</v>
       </c>
@@ -10841,12 +11997,24 @@
       <c r="AK51" s="14" t="n">
         <v>175</v>
       </c>
-      <c r="AL51" s="14" t="n"/>
-      <c r="AM51" s="14" t="n"/>
-      <c r="AN51" s="14" t="n"/>
-      <c r="AO51" s="14" t="n"/>
-      <c r="AP51" s="14" t="n"/>
-      <c r="AQ51" s="14" t="n"/>
+      <c r="AL51" s="14" t="n">
+        <v>3.8581</v>
+      </c>
+      <c r="AM51" s="14" t="n">
+        <v>461.14</v>
+      </c>
+      <c r="AN51" s="14" t="n">
+        <v>187</v>
+      </c>
+      <c r="AO51" s="14" t="n">
+        <v>29245</v>
+      </c>
+      <c r="AP51" s="14" t="n">
+        <v>9921</v>
+      </c>
+      <c r="AQ51" s="14" t="n">
+        <v>19583</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
@@ -10916,22 +12084,22 @@
         </is>
       </c>
       <c r="U52" s="11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V52" s="11" t="n">
         <v>10</v>
       </c>
       <c r="W52" s="11" t="n">
-        <v>2424.2</v>
+        <v>242.4</v>
       </c>
       <c r="X52" s="11" t="n">
-        <v>6896.6</v>
+        <v>689.7</v>
       </c>
       <c r="Y52" s="11" t="n">
-        <v>5333.3</v>
+        <v>533.3</v>
       </c>
       <c r="Z52" s="11" t="n">
-        <v>1600000</v>
+        <v>1600</v>
       </c>
       <c r="AA52" s="11" t="n">
         <v>12</v>
@@ -10942,8 +12110,12 @@
       <c r="AC52" s="11" t="n">
         <v>4080</v>
       </c>
-      <c r="AD52" s="11" t="n"/>
-      <c r="AE52" s="11" t="n"/>
+      <c r="AD52" s="11" t="n">
+        <v>8887.5</v>
+      </c>
+      <c r="AE52" s="11" t="n">
+        <v>22593</v>
+      </c>
       <c r="AF52" s="11" t="n">
         <v>2099</v>
       </c>
@@ -10962,19 +12134,35 @@
       <c r="AK52" s="11" t="n">
         <v>193</v>
       </c>
-      <c r="AL52" s="11" t="n"/>
-      <c r="AM52" s="11" t="n"/>
-      <c r="AN52" s="11" t="n"/>
-      <c r="AO52" s="11" t="n"/>
-      <c r="AP52" s="11" t="n"/>
-      <c r="AQ52" s="11" t="n"/>
+      <c r="AL52" s="11" t="n">
+        <v>4.2549</v>
+      </c>
+      <c r="AM52" s="11" t="n">
+        <v>424.39</v>
+      </c>
+      <c r="AN52" s="11" t="n">
+        <v>173.22</v>
+      </c>
+      <c r="AO52" s="11" t="n">
+        <v>33841</v>
+      </c>
+      <c r="AP52" s="11" t="n">
+        <v>10082</v>
+      </c>
+      <c r="AQ52" s="11" t="n">
+        <v>21961</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n">
         <v>2025</v>
       </c>
-      <c r="B53" s="14" t="n"/>
-      <c r="C53" s="14" t="n"/>
+      <c r="B53" s="14" t="n">
+        <v>3114</v>
+      </c>
+      <c r="C53" s="14" t="n">
+        <v>67</v>
+      </c>
       <c r="D53" s="14" t="n"/>
       <c r="E53" s="14" t="n"/>
       <c r="F53" s="14" t="n"/>
@@ -11027,16 +12215,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="W53" s="14" t="n">
-        <v>3142.9</v>
+        <v>314.3</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>9166.700000000001</v>
+        <v>916.7</v>
       </c>
       <c r="Y53" s="14" t="n">
-        <v>7051.3</v>
+        <v>705.1</v>
       </c>
       <c r="Z53" s="14" t="n">
-        <v>1964285.7</v>
+        <v>1964</v>
       </c>
       <c r="AA53" s="14" t="n">
         <v>13</v>
@@ -11047,8 +12235,12 @@
       <c r="AC53" s="14" t="n">
         <v>3905</v>
       </c>
-      <c r="AD53" s="14" t="n"/>
-      <c r="AE53" s="14" t="n"/>
+      <c r="AD53" s="14" t="n">
+        <v>5764</v>
+      </c>
+      <c r="AE53" s="14" t="n">
+        <v>22593</v>
+      </c>
       <c r="AF53" s="14" t="n">
         <v>2099</v>
       </c>
@@ -11067,12 +12259,24 @@
       <c r="AK53" s="14" t="n">
         <v>245</v>
       </c>
-      <c r="AL53" s="14" t="n"/>
-      <c r="AM53" s="14" t="n"/>
-      <c r="AN53" s="14" t="n"/>
-      <c r="AO53" s="14" t="n"/>
-      <c r="AP53" s="14" t="n"/>
-      <c r="AQ53" s="14" t="n"/>
+      <c r="AL53" s="14" t="n">
+        <v>5.4014</v>
+      </c>
+      <c r="AM53" s="14" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="AN53" s="14" t="n">
+        <v>167.31</v>
+      </c>
+      <c r="AO53" s="14" t="n">
+        <v>18837</v>
+      </c>
+      <c r="AP53" s="14" t="n">
+        <v>9649</v>
+      </c>
+      <c r="AQ53" s="14" t="n">
+        <v>14243</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
